--- a/raw/Timetable_2026Autumn_2026LE.xlsx
+++ b/raw/Timetable_2026Autumn_2026LE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C2282DE-48FC-4586-BF96-557D76597775}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB6C925B-8A5C-4289-9B6A-B6EC4E62E320}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="189">
   <si>
     <t>week</t>
   </si>
@@ -116,30 +116,24 @@
     <t>Tue</t>
   </si>
   <si>
+    <t>2       Sep.</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Programming I (Python)</t>
+  </si>
+  <si>
+    <t>Park Heon Jin</t>
+  </si>
+  <si>
+    <t>B413</t>
+  </si>
+  <si>
     <t>Introduction to Business Administration</t>
   </si>
   <si>
-    <t>Jan Alfred Klingelhöfer</t>
-  </si>
-  <si>
-    <t>B411</t>
-  </si>
-  <si>
-    <t>2       Sep.</t>
-  </si>
-  <si>
-    <t>Wed</t>
-  </si>
-  <si>
-    <t>Programming I (Python)</t>
-  </si>
-  <si>
-    <t>Park Heon Jin</t>
-  </si>
-  <si>
-    <t>B413</t>
-  </si>
-  <si>
     <t xml:space="preserve">Jan Alfred Klingelhöfer </t>
   </si>
   <si>
@@ -156,6 +150,9 @@
   </si>
   <si>
     <t>Fri</t>
+  </si>
+  <si>
+    <t>C303</t>
   </si>
   <si>
     <t>5       Sep.</t>
@@ -313,6 +310,12 @@
     <t>13       Oct.</t>
   </si>
   <si>
+    <t>Jan Alfred Klingelhöfer</t>
+  </si>
+  <si>
+    <t>B411</t>
+  </si>
+  <si>
     <t>14       Oct.</t>
   </si>
   <si>
@@ -387,6 +390,9 @@
   </si>
   <si>
     <t>4       Nov.</t>
+  </si>
+  <si>
+    <t>B409</t>
   </si>
   <si>
     <t>5       Nov.</t>
@@ -608,7 +614,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -654,8 +660,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,6 +701,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -926,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1033,6 +1051,105 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1060,81 +1177,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1451,10 +1500,10 @@
   <cols>
     <col min="1" max="1" width="9.85546875" style="1" customWidth="1"/>
     <col min="2" max="3" width="14.42578125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.85546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.42578125" style="3" customWidth="1"/>
     <col min="5" max="5" width="28.140625" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="41.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="50" style="2" customWidth="1"/>
     <col min="8" max="8" width="28.140625" style="2" customWidth="1"/>
     <col min="9" max="9" width="9.85546875" style="3" customWidth="1"/>
     <col min="10" max="10" width="49.42578125" style="2" customWidth="1"/>
@@ -1487,74 +1536,74 @@
         <v>1</v>
       </c>
       <c r="C2" s="66"/>
-      <c r="D2" s="60" t="s">
+      <c r="D2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="61"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="60" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="61"/>
-      <c r="I2" s="62"/>
-      <c r="J2" s="60" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="62"/>
-      <c r="M2" s="60" t="s">
+      <c r="K2" s="46"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="60" t="s">
+      <c r="N2" s="46"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="62"/>
-      <c r="S2" s="60" t="s">
+      <c r="Q2" s="46"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="61"/>
-      <c r="U2" s="62"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="47"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="64"/>
       <c r="B3" s="67"/>
       <c r="C3" s="68"/>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="61"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="46"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="61"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="60" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="61"/>
-      <c r="L3" s="62"/>
-      <c r="M3" s="60" t="s">
+      <c r="K3" s="46"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="61"/>
-      <c r="O3" s="62"/>
-      <c r="P3" s="60" t="s">
+      <c r="N3" s="46"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="61"/>
-      <c r="R3" s="62"/>
-      <c r="S3" s="60" t="s">
+      <c r="Q3" s="46"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="61"/>
-      <c r="U3" s="62"/>
+      <c r="T3" s="46"/>
+      <c r="U3" s="47"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="45">
+      <c r="A4" s="57">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1608,7 +1657,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="46"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -1625,24 +1674,12 @@
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="9"/>
-      <c r="J5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="9"/>
       <c r="P5" s="6"/>
       <c r="Q5" s="8"/>
       <c r="R5" s="9"/>
@@ -1668,30 +1705,30 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="46"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="F6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>19</v>
@@ -1710,10 +1747,10 @@
       <c r="T6" s="8"/>
       <c r="U6" s="9"/>
       <c r="W6" s="10" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="X6" s="10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y6" s="7">
         <v>44</v>
@@ -1728,12 +1765,12 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="46"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>19</v>
@@ -1745,24 +1782,12 @@
       </c>
       <c r="H7" s="8"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="9"/>
       <c r="P7" s="6"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="9"/>
@@ -1770,7 +1795,7 @@
       <c r="T7" s="8"/>
       <c r="U7" s="9"/>
       <c r="W7" s="10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="X7" s="7"/>
       <c r="Y7" s="7">
@@ -1786,30 +1811,30 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="46"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>33</v>
-      </c>
       <c r="G8" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
@@ -1826,10 +1851,10 @@
       <c r="T8" s="8"/>
       <c r="U8" s="9"/>
       <c r="W8" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="X8" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="7">
         <v>44</v>
@@ -1844,30 +1869,30 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="46"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
       <c r="G9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="9"/>
       <c r="M9" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="9"/>
@@ -1878,7 +1903,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="9"/>
       <c r="W9" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="X9" s="7"/>
       <c r="Y9" s="7">
@@ -1894,12 +1919,12 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="47"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>44</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>45</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8"/>
@@ -1920,10 +1945,10 @@
       <c r="T10" s="8"/>
       <c r="U10" s="9"/>
       <c r="W10" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="X10" s="10" t="s">
         <v>46</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>47</v>
       </c>
       <c r="Y10" s="7">
         <v>48</v>
@@ -1938,11 +1963,11 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="48">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>15</v>
@@ -1982,10 +2007,10 @@
       <c r="T11" s="13"/>
       <c r="U11" s="14"/>
       <c r="W11" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="X11" s="10" t="s">
         <v>49</v>
-      </c>
-      <c r="X11" s="10" t="s">
-        <v>50</v>
       </c>
       <c r="Y11" s="7">
         <v>48</v>
@@ -2000,9 +2025,9 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="49"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>25</v>
@@ -2017,24 +2042,12 @@
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="14"/>
-      <c r="J12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="O12" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="11"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="14"/>
       <c r="P12" s="11"/>
       <c r="Q12" s="13"/>
       <c r="R12" s="14"/>
@@ -2058,30 +2071,30 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="49"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>19</v>
@@ -2094,22 +2107,22 @@
       <c r="N13" s="13"/>
       <c r="O13" s="14"/>
       <c r="P13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="R13" s="14" t="s">
-        <v>55</v>
-      </c>
       <c r="S13" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="T13" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="T13" s="13" t="s">
+      <c r="U13" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>19</v>
@@ -2128,12 +2141,12 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="49"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>19</v>
@@ -2145,24 +2158,12 @@
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="14"/>
-      <c r="J14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M14" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N14" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="O14" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="13"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="11"/>
+      <c r="N14" s="13"/>
+      <c r="O14" s="14"/>
       <c r="P14" s="11"/>
       <c r="Q14" s="13"/>
       <c r="R14" s="14"/>
@@ -2176,30 +2177,30 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="49"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="13"/>
@@ -2217,30 +2218,30 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="49"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
       <c r="G16" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
       <c r="J16" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="14"/>
       <c r="M16" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="14"/>
@@ -2252,12 +2253,12 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="13"/>
@@ -2279,11 +2280,11 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="45">
+      <c r="A18" s="57">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -2324,9 +2325,9 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="46"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>25</v>
@@ -2341,24 +2342,12 @@
       </c>
       <c r="H19" s="8"/>
       <c r="I19" s="9"/>
-      <c r="J19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J19" s="6"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="9"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="8"/>
       <c r="R19" s="9"/>
@@ -2367,30 +2356,30 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="46"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>19</v>
@@ -2403,31 +2392,31 @@
       <c r="N20" s="8"/>
       <c r="O20" s="9"/>
       <c r="P20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="R20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R20" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="S20" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T20" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="T20" s="8" t="s">
+      <c r="U20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="U20" s="9" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="46"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>19</v>
@@ -2439,24 +2428,12 @@
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="9"/>
-      <c r="J21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N21" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J21" s="6"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="9"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="8"/>
       <c r="R21" s="9"/>
@@ -2465,30 +2442,30 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="8"/>
@@ -2506,12 +2483,12 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="46"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="16"/>
@@ -2533,31 +2510,19 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="47"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="I24" s="22" t="s">
-        <v>28</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="22"/>
       <c r="J24" s="23"/>
       <c r="K24" s="23"/>
       <c r="L24" s="24"/>
@@ -2572,11 +2537,11 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="48">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>15</v>
@@ -2617,9 +2582,9 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="49"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>25</v>
@@ -2634,24 +2599,12 @@
       </c>
       <c r="H26" s="13"/>
       <c r="I26" s="14"/>
-      <c r="J26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K26" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="N26" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="O26" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J26" s="11"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="13"/>
+      <c r="O26" s="14"/>
       <c r="P26" s="11"/>
       <c r="Q26" s="13"/>
       <c r="R26" s="14"/>
@@ -2660,30 +2613,30 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="49"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>19</v>
@@ -2696,31 +2649,31 @@
       <c r="N27" s="13"/>
       <c r="O27" s="14"/>
       <c r="P27" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="Q27" s="13" t="s">
+      <c r="R27" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="R27" s="14" t="s">
-        <v>55</v>
-      </c>
       <c r="S27" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="T27" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="T27" s="13" t="s">
+      <c r="U27" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U27" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="49"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>19</v>
@@ -2732,24 +2685,12 @@
       </c>
       <c r="H28" s="13"/>
       <c r="I28" s="14"/>
-      <c r="J28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="K28" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="M28" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="N28" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="O28" s="14" t="s">
-        <v>28</v>
-      </c>
+      <c r="J28" s="11"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="14"/>
       <c r="P28" s="11"/>
       <c r="Q28" s="13"/>
       <c r="R28" s="14"/>
@@ -2758,94 +2699,94 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="49"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="48" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="51" t="s">
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="49"/>
+      <c r="J29" s="49"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="50"/>
+    </row>
+    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="61"/>
+      <c r="B30" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="53"/>
-    </row>
-    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="49"/>
-      <c r="B30" s="28" t="s">
+      <c r="C30" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="51"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52"/>
+      <c r="J30" s="52"/>
+      <c r="K30" s="52"/>
+      <c r="L30" s="52"/>
+      <c r="M30" s="52"/>
+      <c r="N30" s="52"/>
+      <c r="O30" s="52"/>
+      <c r="P30" s="52"/>
+      <c r="Q30" s="52"/>
+      <c r="R30" s="52"/>
+      <c r="S30" s="52"/>
+      <c r="T30" s="52"/>
+      <c r="U30" s="53"/>
+    </row>
+    <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="62"/>
+      <c r="B31" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="56"/>
-    </row>
-    <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="50"/>
-      <c r="B31" s="28" t="s">
+      <c r="C31" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="54"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="55"/>
+      <c r="J31" s="55"/>
+      <c r="K31" s="55"/>
+      <c r="L31" s="55"/>
+      <c r="M31" s="55"/>
+      <c r="N31" s="55"/>
+      <c r="O31" s="55"/>
+      <c r="P31" s="55"/>
+      <c r="Q31" s="55"/>
+      <c r="R31" s="55"/>
+      <c r="S31" s="55"/>
+      <c r="T31" s="55"/>
+      <c r="U31" s="56"/>
+    </row>
+    <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="57">
+        <v>5</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
-    </row>
-    <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="45">
-        <v>5</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>75</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>15</v>
@@ -2886,9 +2827,9 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="46"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>25</v>
@@ -2903,24 +2844,12 @@
       </c>
       <c r="H33" s="8"/>
       <c r="I33" s="9"/>
-      <c r="J33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>28</v>
-      </c>
+      <c r="J33" s="6"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="8"/>
+      <c r="O33" s="9"/>
       <c r="P33" s="6"/>
       <c r="Q33" s="8"/>
       <c r="R33" s="9"/>
@@ -2929,30 +2858,30 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="46"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>19</v>
@@ -2972,205 +2901,205 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="46"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="30" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="48" t="s">
+        <v>71</v>
+      </c>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="49"/>
+      <c r="J35" s="49"/>
+      <c r="K35" s="49"/>
+      <c r="L35" s="49"/>
+      <c r="M35" s="49"/>
+      <c r="N35" s="49"/>
+      <c r="O35" s="49"/>
+      <c r="P35" s="49"/>
+      <c r="Q35" s="49"/>
+      <c r="R35" s="49"/>
+      <c r="S35" s="49"/>
+      <c r="T35" s="49"/>
+      <c r="U35" s="50"/>
+    </row>
+    <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="58"/>
+      <c r="B36" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D35" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="53"/>
-    </row>
-    <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="46"/>
-      <c r="B36" s="30" t="s">
+      <c r="C36" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="D36" s="51"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+      <c r="K36" s="52"/>
+      <c r="L36" s="52"/>
+      <c r="M36" s="52"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="52"/>
+      <c r="P36" s="52"/>
+      <c r="Q36" s="52"/>
+      <c r="R36" s="52"/>
+      <c r="S36" s="52"/>
+      <c r="T36" s="52"/>
+      <c r="U36" s="53"/>
+    </row>
+    <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="58"/>
+      <c r="B37" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="56"/>
-    </row>
-    <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="46"/>
-      <c r="B37" s="30" t="s">
+      <c r="C37" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="51"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52"/>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="52"/>
+      <c r="L37" s="52"/>
+      <c r="M37" s="52"/>
+      <c r="N37" s="52"/>
+      <c r="O37" s="52"/>
+      <c r="P37" s="52"/>
+      <c r="Q37" s="52"/>
+      <c r="R37" s="52"/>
+      <c r="S37" s="52"/>
+      <c r="T37" s="52"/>
+      <c r="U37" s="53"/>
+    </row>
+    <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="59"/>
+      <c r="B38" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="56"/>
-    </row>
-    <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="47"/>
-      <c r="B38" s="30" t="s">
+      <c r="C38" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="51"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52"/>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52"/>
+      <c r="J38" s="52"/>
+      <c r="K38" s="52"/>
+      <c r="L38" s="52"/>
+      <c r="M38" s="52"/>
+      <c r="N38" s="52"/>
+      <c r="O38" s="52"/>
+      <c r="P38" s="52"/>
+      <c r="Q38" s="52"/>
+      <c r="R38" s="52"/>
+      <c r="S38" s="52"/>
+      <c r="T38" s="52"/>
+      <c r="U38" s="53"/>
+    </row>
+    <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="60">
+        <v>6</v>
+      </c>
+      <c r="B39" s="30" t="s">
         <v>81</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="55"/>
-      <c r="R38" s="55"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="56"/>
-    </row>
-    <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="48">
-        <v>6</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>82</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="56"/>
+      <c r="D39" s="51"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
+      <c r="Q39" s="52"/>
+      <c r="R39" s="52"/>
+      <c r="S39" s="52"/>
+      <c r="T39" s="52"/>
+      <c r="U39" s="53"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="49"/>
+      <c r="A40" s="61"/>
       <c r="B40" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="56"/>
+      <c r="D40" s="51"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="52"/>
+      <c r="K40" s="52"/>
+      <c r="L40" s="52"/>
+      <c r="M40" s="52"/>
+      <c r="N40" s="52"/>
+      <c r="O40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="53"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="49"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="55"/>
+      <c r="N41" s="55"/>
+      <c r="O41" s="55"/>
+      <c r="P41" s="55"/>
+      <c r="Q41" s="55"/>
+      <c r="R41" s="55"/>
+      <c r="S41" s="55"/>
+      <c r="T41" s="55"/>
+      <c r="U41" s="56"/>
+    </row>
+    <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="61"/>
+      <c r="B42" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C41" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
-    </row>
-    <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="49"/>
-      <c r="B42" s="31" t="s">
-        <v>85</v>
-      </c>
       <c r="C42" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>19</v>
@@ -3196,12 +3125,12 @@
       <c r="U42" s="14"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="49"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D43" s="11"/>
       <c r="E43" s="13"/>
@@ -3225,12 +3154,12 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="49"/>
+      <c r="A44" s="61"/>
       <c r="B44" s="32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="23"/>
@@ -3252,12 +3181,12 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="13"/>
@@ -3279,11 +3208,11 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="45">
+      <c r="A46" s="57">
         <v>7</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
@@ -3324,9 +3253,9 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="46"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>25</v>
@@ -3342,22 +3271,22 @@
       <c r="H47" s="8"/>
       <c r="I47" s="9"/>
       <c r="J47" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N47" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="8"/>
@@ -3367,30 +3296,30 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="46"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="33" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>19</v>
@@ -3410,12 +3339,12 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="46"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="33" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>19</v>
@@ -3428,22 +3357,22 @@
       <c r="H49" s="8"/>
       <c r="I49" s="9"/>
       <c r="J49" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N49" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="8"/>
@@ -3453,30 +3382,30 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="46"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="8"/>
@@ -3494,30 +3423,30 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="46"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="33" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
       <c r="G51" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="9"/>
       <c r="J51" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="9"/>
       <c r="M51" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="9"/>
@@ -3529,12 +3458,12 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="47"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="33" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="8"/>
@@ -3556,11 +3485,11 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="48">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
@@ -3601,9 +3530,9 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="49"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="31" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>25</v>
@@ -3619,22 +3548,22 @@
       <c r="H54" s="13"/>
       <c r="I54" s="14"/>
       <c r="J54" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K54" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K54" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L54" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M54" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N54" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N54" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O54" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P54" s="11"/>
       <c r="Q54" s="13"/>
@@ -3644,30 +3573,30 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="49"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="31" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>19</v>
@@ -3680,31 +3609,31 @@
       <c r="N55" s="13"/>
       <c r="O55" s="14"/>
       <c r="P55" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q55" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="Q55" s="13" t="s">
+      <c r="R55" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="R55" s="14" t="s">
-        <v>55</v>
-      </c>
       <c r="S55" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="T55" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="T55" s="13" t="s">
+      <c r="U55" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="U55" s="14" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="49"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="31" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>19</v>
@@ -3717,22 +3646,22 @@
       <c r="H56" s="13"/>
       <c r="I56" s="14"/>
       <c r="J56" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K56" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K56" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L56" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M56" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N56" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N56" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O56" s="14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P56" s="11"/>
       <c r="Q56" s="13"/>
@@ -3742,30 +3671,30 @@
       <c r="U56" s="14"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="49"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>20</v>
@@ -3785,30 +3714,30 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="49"/>
+      <c r="A58" s="61"/>
       <c r="B58" s="31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>42</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
       <c r="G58" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="14"/>
       <c r="J58" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K58" s="13"/>
       <c r="L58" s="14"/>
       <c r="M58" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N58" s="13"/>
       <c r="O58" s="14"/>
@@ -3820,12 +3749,12 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="50"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="31" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="13"/>
@@ -3847,11 +3776,11 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="45">
+      <c r="A60" s="57">
         <v>9</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
@@ -3892,9 +3821,9 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="46"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="33" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>25</v>
@@ -3910,22 +3839,22 @@
       <c r="H61" s="8"/>
       <c r="I61" s="9"/>
       <c r="J61" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="K61" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="N61" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="8"/>
@@ -3935,30 +3864,30 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="46"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>19</v>
@@ -3971,31 +3900,31 @@
       <c r="N62" s="8"/>
       <c r="O62" s="9"/>
       <c r="P62" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q62" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q62" s="8" t="s">
+      <c r="R62" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R62" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="S62" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T62" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="T62" s="8" t="s">
+      <c r="U62" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="U62" s="9" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="46"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="33" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>19</v>
@@ -4008,22 +3937,22 @@
       <c r="H63" s="8"/>
       <c r="I63" s="9"/>
       <c r="J63" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K63" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N63" s="8" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="8"/>
@@ -4033,30 +3962,30 @@
       <c r="U63" s="34"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="46"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>20</v>
@@ -4076,30 +4005,30 @@
       <c r="U64" s="34"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="46"/>
+      <c r="A65" s="58"/>
       <c r="B65" s="33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="9"/>
       <c r="G65" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K65" s="8"/>
       <c r="L65" s="9"/>
       <c r="M65" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N65" s="8"/>
       <c r="O65" s="9"/>
@@ -4111,12 +4040,12 @@
       <c r="U65" s="34"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="47"/>
+      <c r="A66" s="59"/>
       <c r="B66" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="8"/>
@@ -4138,11 +4067,11 @@
       <c r="U66" s="34"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="48">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>15</v>
@@ -4183,9 +4112,9 @@
       <c r="U67" s="35"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="49"/>
+      <c r="A68" s="61"/>
       <c r="B68" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>25</v>
@@ -4201,22 +4130,22 @@
       <c r="H68" s="13"/>
       <c r="I68" s="14"/>
       <c r="J68" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K68" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K68" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L68" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M68" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N68" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N68" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O68" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P68" s="11"/>
       <c r="Q68" s="13"/>
@@ -4226,30 +4155,30 @@
       <c r="U68" s="35"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="49"/>
+      <c r="A69" s="61"/>
       <c r="B69" s="31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>19</v>
@@ -4269,12 +4198,12 @@
       <c r="U69" s="35"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="49"/>
+      <c r="A70" s="61"/>
       <c r="B70" s="31" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>19</v>
@@ -4287,22 +4216,22 @@
       <c r="H70" s="13"/>
       <c r="I70" s="14"/>
       <c r="J70" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K70" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K70" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L70" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M70" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N70" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N70" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O70" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P70" s="11"/>
       <c r="Q70" s="13"/>
@@ -4312,30 +4241,30 @@
       <c r="U70" s="35"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="49"/>
+      <c r="A71" s="61"/>
       <c r="B71" s="31" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E71" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H71" s="13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>20</v>
@@ -4355,12 +4284,12 @@
       <c r="U71" s="35"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="49"/>
+      <c r="A72" s="61"/>
       <c r="B72" s="31" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="13"/>
@@ -4382,12 +4311,12 @@
       <c r="U72" s="35"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="50"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="13"/>
@@ -4409,11 +4338,11 @@
       <c r="U73" s="35"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="45">
+      <c r="A74" s="57">
         <v>11</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -4454,9 +4383,9 @@
       <c r="U74" s="34"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="46"/>
+      <c r="A75" s="58"/>
       <c r="B75" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>25</v>
@@ -4472,22 +4401,22 @@
       <c r="H75" s="8"/>
       <c r="I75" s="9"/>
       <c r="J75" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K75" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K75" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L75" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M75" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N75" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N75" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O75" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="8"/>
@@ -4497,19 +4426,31 @@
       <c r="U75" s="34"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="46"/>
+      <c r="A76" s="58"/>
       <c r="B76" s="33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D76" s="6"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="9"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F76" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I76" s="79" t="s">
+        <v>117</v>
+      </c>
       <c r="J76" s="6" t="s">
         <v>19</v>
       </c>
@@ -4521,31 +4462,31 @@
       <c r="N76" s="8"/>
       <c r="O76" s="9"/>
       <c r="P76" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q76" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="Q76" s="8" t="s">
+      <c r="R76" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="R76" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="S76" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="T76" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="T76" s="8" t="s">
+      <c r="U76" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="U76" s="9" t="s">
-        <v>55</v>
-      </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="46"/>
+      <c r="A77" s="58"/>
       <c r="B77" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>19</v>
@@ -4558,22 +4499,22 @@
       <c r="H77" s="8"/>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K77" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K77" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L77" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M77" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N77" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N77" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O77" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="8"/>
@@ -4583,19 +4524,31 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="46"/>
+      <c r="A78" s="58"/>
       <c r="B78" s="33" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D78" s="6"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="8"/>
-      <c r="I78" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F78" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I78" s="78" t="s">
+        <v>117</v>
+      </c>
       <c r="J78" s="6" t="s">
         <v>20</v>
       </c>
@@ -4614,12 +4567,12 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="46"/>
+      <c r="A79" s="58"/>
       <c r="B79" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D79" s="6"/>
       <c r="E79" s="8"/>
@@ -4641,12 +4594,12 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="47"/>
+      <c r="A80" s="59"/>
       <c r="B80" s="33" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="8"/>
@@ -4668,11 +4621,11 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="48">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="31" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C81" s="12" t="s">
         <v>15</v>
@@ -4713,9 +4666,9 @@
       <c r="U81" s="14"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="49"/>
+      <c r="A82" s="61"/>
       <c r="B82" s="31" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>25</v>
@@ -4724,29 +4677,29 @@
         <v>19</v>
       </c>
       <c r="E82" s="13"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="13"/>
-      <c r="I82" s="14"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="39"/>
+      <c r="I82" s="40"/>
       <c r="J82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K82" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K82" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L82" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M82" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N82" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N82" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O82" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P82" s="11"/>
       <c r="Q82" s="13"/>
@@ -4756,20 +4709,32 @@
       <c r="U82" s="14"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="49"/>
+      <c r="A83" s="61"/>
       <c r="B83" s="31" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D83" s="11"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="14"/>
-      <c r="G83" s="11"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E83" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="F83" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G83" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H83" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="I83" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J83" s="13" t="s">
         <v>19</v>
       </c>
       <c r="K83" s="13"/>
@@ -4780,59 +4745,59 @@
       <c r="N83" s="13"/>
       <c r="O83" s="14"/>
       <c r="P83" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q83" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T83" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U83" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="49"/>
+      <c r="A84" s="61"/>
       <c r="B84" s="31" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D84" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="E84" s="13"/>
-      <c r="F84" s="14"/>
-      <c r="G84" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="13"/>
+      <c r="E84" s="39"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="36"/>
       <c r="I84" s="14"/>
       <c r="J84" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K84" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K84" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="L84" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M84" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N84" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="N84" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="O84" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P84" s="11"/>
       <c r="Q84" s="13"/>
@@ -4842,20 +4807,32 @@
       <c r="U84" s="14"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="49"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="31" t="s">
-        <v>133</v>
-      </c>
-      <c r="C85" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D85" s="11"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="14"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="C85" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D85" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E85" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="F85" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G85" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="H85" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="I85" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J85" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K85" s="13"/>
@@ -4873,30 +4850,30 @@
       <c r="U85" s="14"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="49"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="31" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D86" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D86" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="E86" s="13"/>
-      <c r="F86" s="14"/>
-      <c r="G86" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H86" s="13"/>
-      <c r="I86" s="14"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="H86" s="26"/>
+      <c r="I86" s="27"/>
       <c r="J86" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K86" s="13"/>
       <c r="L86" s="14"/>
       <c r="M86" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N86" s="13"/>
       <c r="O86" s="14"/>
@@ -4908,12 +4885,12 @@
       <c r="U86" s="14"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="50"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="31" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D87" s="11"/>
       <c r="E87" s="13"/>
@@ -4935,11 +4912,11 @@
       <c r="U87" s="14"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="45">
+      <c r="A88" s="57">
         <v>13</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>15</v>
@@ -4980,9 +4957,9 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="46"/>
+      <c r="A89" s="58"/>
       <c r="B89" s="33" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>25</v>
@@ -4998,22 +4975,22 @@
       <c r="H89" s="8"/>
       <c r="I89" s="9"/>
       <c r="J89" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K89" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K89" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L89" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M89" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N89" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N89" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O89" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="8"/>
@@ -5023,19 +5000,31 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="46"/>
+      <c r="A90" s="58"/>
       <c r="B90" s="33" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D90" s="6"/>
-      <c r="E90" s="8"/>
-      <c r="F90" s="9"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="8"/>
-      <c r="I90" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F90" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I90" s="78" t="s">
+        <v>117</v>
+      </c>
       <c r="J90" s="6" t="s">
         <v>19</v>
       </c>
@@ -5047,31 +5036,31 @@
       <c r="N90" s="8"/>
       <c r="O90" s="9"/>
       <c r="P90" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R90" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S90" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U90" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="46"/>
+      <c r="A91" s="58"/>
       <c r="B91" s="33" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>19</v>
@@ -5084,22 +5073,22 @@
       <c r="H91" s="8"/>
       <c r="I91" s="9"/>
       <c r="J91" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K91" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K91" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L91" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M91" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N91" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N91" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O91" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P91" s="6"/>
       <c r="Q91" s="8"/>
@@ -5109,19 +5098,31 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="46"/>
+      <c r="A92" s="58"/>
       <c r="B92" s="33" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D92" s="6"/>
-      <c r="E92" s="8"/>
-      <c r="F92" s="9"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="8"/>
-      <c r="I92" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F92" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I92" s="78" t="s">
+        <v>117</v>
+      </c>
       <c r="J92" s="6" t="s">
         <v>20</v>
       </c>
@@ -5140,30 +5141,30 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="46"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="33" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C93" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="9"/>
       <c r="G93" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
       <c r="J93" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K93" s="8"/>
       <c r="L93" s="9"/>
       <c r="M93" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="9"/>
@@ -5175,12 +5176,12 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="47"/>
+      <c r="A94" s="59"/>
       <c r="B94" s="33" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="8"/>
@@ -5202,11 +5203,11 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="48">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="31" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>15</v>
@@ -5247,9 +5248,9 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="49"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="31" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>25</v>
@@ -5264,12 +5265,22 @@
       </c>
       <c r="H96" s="13"/>
       <c r="I96" s="14"/>
-      <c r="J96" s="11"/>
-      <c r="K96" s="13"/>
-      <c r="L96" s="14"/>
-      <c r="M96" s="11"/>
-      <c r="N96" s="13"/>
-      <c r="O96" s="14"/>
+      <c r="J96" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K96" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L96" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M96" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="N96" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="O96" s="43"/>
       <c r="P96" s="11"/>
       <c r="Q96" s="13"/>
       <c r="R96" s="14"/>
@@ -5278,30 +5289,30 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="49"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="31" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D97" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E97" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E97" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="F97" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G97" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H97" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H97" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I97" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J97" s="11" t="s">
         <v>19</v>
@@ -5314,31 +5325,31 @@
       <c r="N97" s="13"/>
       <c r="O97" s="14"/>
       <c r="P97" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q97" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R97" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S97" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T97" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U97" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="49"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="31" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D98" s="11" t="s">
         <v>19</v>
@@ -5350,12 +5361,22 @@
       </c>
       <c r="H98" s="13"/>
       <c r="I98" s="14"/>
-      <c r="J98" s="11"/>
-      <c r="K98" s="13"/>
-      <c r="L98" s="14"/>
-      <c r="M98" s="11"/>
-      <c r="N98" s="13"/>
-      <c r="O98" s="14"/>
+      <c r="J98" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K98" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="L98" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="M98" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="N98" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="O98" s="43"/>
       <c r="P98" s="11"/>
       <c r="Q98" s="13"/>
       <c r="R98" s="14"/>
@@ -5364,30 +5385,30 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="49"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E99" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F99" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="C99" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="D99" s="11" t="s">
+      <c r="G99" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H99" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E99" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="F99" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="G99" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I99" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J99" s="11" t="s">
         <v>20</v>
@@ -5407,48 +5428,48 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="49"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="31" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D100" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E100" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E100" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="F100" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G100" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H100" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I100" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J100" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K100" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K100" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="L100" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M100" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N100" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N100" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="O100" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P100" s="11"/>
       <c r="Q100" s="13"/>
@@ -5458,12 +5479,12 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="50"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="31" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D101" s="11"/>
       <c r="E101" s="13"/>
@@ -5485,11 +5506,11 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="45">
+      <c r="A102" s="57">
         <v>15</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>15</v>
@@ -5530,9 +5551,9 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="46"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="33" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>25</v>
@@ -5548,22 +5569,22 @@
       <c r="H103" s="8"/>
       <c r="I103" s="9"/>
       <c r="J103" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K103" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K103" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="L103" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M103" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N103" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="N103" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="O103" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P103" s="6"/>
       <c r="Q103" s="8"/>
@@ -5573,30 +5594,30 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="46"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="33" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E104" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E104" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="F104" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H104" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H104" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="I104" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J104" s="6" t="s">
         <v>19</v>
@@ -5609,31 +5630,31 @@
       <c r="N104" s="8"/>
       <c r="O104" s="9"/>
       <c r="P104" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q104" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R104" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S104" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T104" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U104" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="46"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="33" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>19</v>
@@ -5646,22 +5667,22 @@
       <c r="H105" s="8"/>
       <c r="I105" s="9"/>
       <c r="J105" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K105" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="K105" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="L105" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M105" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="N105" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="N105" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="O105" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P105" s="6"/>
       <c r="Q105" s="8"/>
@@ -5671,30 +5692,30 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="46"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D106" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E106" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E106" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="F106" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H106" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="H106" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="I106" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>20</v>
@@ -5714,30 +5735,30 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="46"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D107" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>42</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="9"/>
       <c r="G107" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="9"/>
       <c r="J107" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K107" s="8"/>
       <c r="L107" s="9"/>
       <c r="M107" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N107" s="8"/>
       <c r="O107" s="9"/>
@@ -5749,12 +5770,12 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="47"/>
+      <c r="A108" s="59"/>
       <c r="B108" s="33" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="8"/>
@@ -5776,11 +5797,11 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="48">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="31" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>15</v>
@@ -5821,9 +5842,9 @@
       <c r="U109" s="35"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="49"/>
+      <c r="A110" s="61"/>
       <c r="B110" s="31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>25</v>
@@ -5839,22 +5860,22 @@
       <c r="H110" s="13"/>
       <c r="I110" s="14"/>
       <c r="J110" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K110" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K110" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="L110" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M110" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N110" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N110" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="O110" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P110" s="11"/>
       <c r="Q110" s="13"/>
@@ -5864,30 +5885,30 @@
       <c r="U110" s="35"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="49"/>
+      <c r="A111" s="61"/>
       <c r="B111" s="31" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D111" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E111" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E111" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="F111" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G111" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H111" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H111" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I111" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J111" s="11" t="s">
         <v>19</v>
@@ -5900,31 +5921,31 @@
       <c r="N111" s="13"/>
       <c r="O111" s="14"/>
       <c r="P111" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q111" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R111" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S111" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T111" s="13" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U111" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="49"/>
+      <c r="A112" s="61"/>
       <c r="B112" s="31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>19</v>
@@ -5937,22 +5958,22 @@
       <c r="H112" s="13"/>
       <c r="I112" s="14"/>
       <c r="J112" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K112" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="K112" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="L112" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M112" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N112" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="N112" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="O112" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P112" s="11"/>
       <c r="Q112" s="13"/>
@@ -5962,30 +5983,30 @@
       <c r="U112" s="35"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="49"/>
+      <c r="A113" s="61"/>
       <c r="B113" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D113" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E113" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E113" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="F113" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G113" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="H113" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H113" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I113" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J113" s="11" t="s">
         <v>20</v>
@@ -6005,12 +6026,12 @@
       <c r="U113" s="35"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="49"/>
+      <c r="A114" s="61"/>
       <c r="B114" s="31" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="13"/>
@@ -6032,12 +6053,12 @@
       <c r="U114" s="35"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="50"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="31" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="13"/>
@@ -6059,11 +6080,11 @@
       <c r="U115" s="35"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="45">
+      <c r="A116" s="57">
         <v>17</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>15</v>
@@ -6102,9 +6123,9 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="46"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="33" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>25</v>
@@ -6118,22 +6139,22 @@
       <c r="H117" s="8"/>
       <c r="I117" s="9"/>
       <c r="J117" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K117" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K117" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L117" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M117" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N117" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N117" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O117" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P117" s="6"/>
       <c r="Q117" s="8"/>
@@ -6143,19 +6164,31 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="46"/>
+      <c r="A118" s="58"/>
       <c r="B118" s="33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D118" s="6"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="8"/>
-      <c r="I118" s="9"/>
+        <v>27</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E118" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F118" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G118" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I118" s="78" t="s">
+        <v>117</v>
+      </c>
       <c r="J118" s="6"/>
       <c r="K118" s="8"/>
       <c r="L118" s="9"/>
@@ -6165,31 +6198,31 @@
       <c r="N118" s="8"/>
       <c r="O118" s="9"/>
       <c r="P118" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="R118" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="S118" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="T118" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="U118" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="46"/>
+      <c r="A119" s="58"/>
       <c r="B119" s="33" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D119" s="6"/>
       <c r="E119" s="8"/>
@@ -6200,22 +6233,22 @@
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
       <c r="J119" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="K119" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="K119" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="L119" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M119" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N119" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="N119" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="O119" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P119" s="6"/>
       <c r="Q119" s="8"/>
@@ -6225,19 +6258,31 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="46"/>
+      <c r="A120" s="58"/>
       <c r="B120" s="33" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D120" s="6"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="9"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="9"/>
+        <v>37</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E120" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F120" s="78" t="s">
+        <v>117</v>
+      </c>
+      <c r="G120" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I120" s="78" t="s">
+        <v>117</v>
+      </c>
       <c r="J120" s="6" t="s">
         <v>20</v>
       </c>
@@ -6256,12 +6301,12 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="46"/>
+      <c r="A121" s="58"/>
       <c r="B121" s="33" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="8"/>
@@ -6283,12 +6328,12 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="47"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="33" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="8"/>
@@ -6310,388 +6355,388 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="48">
+      <c r="A123" s="60">
         <v>18</v>
       </c>
       <c r="B123" s="31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C123" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="36" t="s">
-        <v>173</v>
-      </c>
-      <c r="E123" s="37"/>
-      <c r="F123" s="37"/>
-      <c r="G123" s="37"/>
-      <c r="H123" s="37"/>
-      <c r="I123" s="37"/>
-      <c r="J123" s="37"/>
-      <c r="K123" s="37"/>
-      <c r="L123" s="37"/>
-      <c r="M123" s="37"/>
-      <c r="N123" s="37"/>
-      <c r="O123" s="37"/>
-      <c r="P123" s="37"/>
-      <c r="Q123" s="37"/>
-      <c r="R123" s="37"/>
-      <c r="S123" s="37"/>
-      <c r="T123" s="37"/>
-      <c r="U123" s="38"/>
+      <c r="D123" s="69" t="s">
+        <v>175</v>
+      </c>
+      <c r="E123" s="70"/>
+      <c r="F123" s="70"/>
+      <c r="G123" s="70"/>
+      <c r="H123" s="70"/>
+      <c r="I123" s="70"/>
+      <c r="J123" s="70"/>
+      <c r="K123" s="70"/>
+      <c r="L123" s="70"/>
+      <c r="M123" s="70"/>
+      <c r="N123" s="70"/>
+      <c r="O123" s="70"/>
+      <c r="P123" s="70"/>
+      <c r="Q123" s="70"/>
+      <c r="R123" s="70"/>
+      <c r="S123" s="70"/>
+      <c r="T123" s="70"/>
+      <c r="U123" s="71"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="49"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="31" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="39"/>
-      <c r="E124" s="40"/>
-      <c r="F124" s="40"/>
-      <c r="G124" s="40"/>
-      <c r="H124" s="40"/>
-      <c r="I124" s="40"/>
-      <c r="J124" s="40"/>
-      <c r="K124" s="40"/>
-      <c r="L124" s="40"/>
-      <c r="M124" s="40"/>
-      <c r="N124" s="40"/>
-      <c r="O124" s="40"/>
-      <c r="P124" s="40"/>
-      <c r="Q124" s="40"/>
-      <c r="R124" s="40"/>
-      <c r="S124" s="40"/>
-      <c r="T124" s="40"/>
-      <c r="U124" s="41"/>
+      <c r="D124" s="72"/>
+      <c r="E124" s="73"/>
+      <c r="F124" s="73"/>
+      <c r="G124" s="73"/>
+      <c r="H124" s="73"/>
+      <c r="I124" s="73"/>
+      <c r="J124" s="73"/>
+      <c r="K124" s="73"/>
+      <c r="L124" s="73"/>
+      <c r="M124" s="73"/>
+      <c r="N124" s="73"/>
+      <c r="O124" s="73"/>
+      <c r="P124" s="73"/>
+      <c r="Q124" s="73"/>
+      <c r="R124" s="73"/>
+      <c r="S124" s="73"/>
+      <c r="T124" s="73"/>
+      <c r="U124" s="74"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="49"/>
+      <c r="A125" s="61"/>
       <c r="B125" s="31" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D125" s="39"/>
-      <c r="E125" s="40"/>
-      <c r="F125" s="40"/>
-      <c r="G125" s="40"/>
-      <c r="H125" s="40"/>
-      <c r="I125" s="40"/>
-      <c r="J125" s="40"/>
-      <c r="K125" s="40"/>
-      <c r="L125" s="40"/>
-      <c r="M125" s="40"/>
-      <c r="N125" s="40"/>
-      <c r="O125" s="40"/>
-      <c r="P125" s="40"/>
-      <c r="Q125" s="40"/>
-      <c r="R125" s="40"/>
-      <c r="S125" s="40"/>
-      <c r="T125" s="40"/>
-      <c r="U125" s="41"/>
+        <v>27</v>
+      </c>
+      <c r="D125" s="72"/>
+      <c r="E125" s="73"/>
+      <c r="F125" s="73"/>
+      <c r="G125" s="73"/>
+      <c r="H125" s="73"/>
+      <c r="I125" s="73"/>
+      <c r="J125" s="73"/>
+      <c r="K125" s="73"/>
+      <c r="L125" s="73"/>
+      <c r="M125" s="73"/>
+      <c r="N125" s="73"/>
+      <c r="O125" s="73"/>
+      <c r="P125" s="73"/>
+      <c r="Q125" s="73"/>
+      <c r="R125" s="73"/>
+      <c r="S125" s="73"/>
+      <c r="T125" s="73"/>
+      <c r="U125" s="74"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="49"/>
+      <c r="A126" s="61"/>
       <c r="B126" s="31" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D126" s="39"/>
-      <c r="E126" s="40"/>
-      <c r="F126" s="40"/>
-      <c r="G126" s="40"/>
-      <c r="H126" s="40"/>
-      <c r="I126" s="40"/>
-      <c r="J126" s="40"/>
-      <c r="K126" s="40"/>
-      <c r="L126" s="40"/>
-      <c r="M126" s="40"/>
-      <c r="N126" s="40"/>
-      <c r="O126" s="40"/>
-      <c r="P126" s="40"/>
-      <c r="Q126" s="40"/>
-      <c r="R126" s="40"/>
-      <c r="S126" s="40"/>
-      <c r="T126" s="40"/>
-      <c r="U126" s="41"/>
+        <v>34</v>
+      </c>
+      <c r="D126" s="72"/>
+      <c r="E126" s="73"/>
+      <c r="F126" s="73"/>
+      <c r="G126" s="73"/>
+      <c r="H126" s="73"/>
+      <c r="I126" s="73"/>
+      <c r="J126" s="73"/>
+      <c r="K126" s="73"/>
+      <c r="L126" s="73"/>
+      <c r="M126" s="73"/>
+      <c r="N126" s="73"/>
+      <c r="O126" s="73"/>
+      <c r="P126" s="73"/>
+      <c r="Q126" s="73"/>
+      <c r="R126" s="73"/>
+      <c r="S126" s="73"/>
+      <c r="T126" s="73"/>
+      <c r="U126" s="74"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="49"/>
+      <c r="A127" s="61"/>
       <c r="B127" s="30" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C127" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D127" s="39"/>
-      <c r="E127" s="40"/>
-      <c r="F127" s="40"/>
-      <c r="G127" s="40"/>
-      <c r="H127" s="40"/>
-      <c r="I127" s="40"/>
-      <c r="J127" s="40"/>
-      <c r="K127" s="40"/>
-      <c r="L127" s="40"/>
-      <c r="M127" s="40"/>
-      <c r="N127" s="40"/>
-      <c r="O127" s="40"/>
-      <c r="P127" s="40"/>
-      <c r="Q127" s="40"/>
-      <c r="R127" s="40"/>
-      <c r="S127" s="40"/>
-      <c r="T127" s="40"/>
-      <c r="U127" s="41"/>
+        <v>37</v>
+      </c>
+      <c r="D127" s="72"/>
+      <c r="E127" s="73"/>
+      <c r="F127" s="73"/>
+      <c r="G127" s="73"/>
+      <c r="H127" s="73"/>
+      <c r="I127" s="73"/>
+      <c r="J127" s="73"/>
+      <c r="K127" s="73"/>
+      <c r="L127" s="73"/>
+      <c r="M127" s="73"/>
+      <c r="N127" s="73"/>
+      <c r="O127" s="73"/>
+      <c r="P127" s="73"/>
+      <c r="Q127" s="73"/>
+      <c r="R127" s="73"/>
+      <c r="S127" s="73"/>
+      <c r="T127" s="73"/>
+      <c r="U127" s="74"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="49"/>
+      <c r="A128" s="61"/>
       <c r="B128" s="31" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D128" s="39"/>
-      <c r="E128" s="40"/>
-      <c r="F128" s="40"/>
-      <c r="G128" s="40"/>
-      <c r="H128" s="40"/>
-      <c r="I128" s="40"/>
-      <c r="J128" s="40"/>
-      <c r="K128" s="40"/>
-      <c r="L128" s="40"/>
-      <c r="M128" s="40"/>
-      <c r="N128" s="40"/>
-      <c r="O128" s="40"/>
-      <c r="P128" s="40"/>
-      <c r="Q128" s="40"/>
-      <c r="R128" s="40"/>
-      <c r="S128" s="40"/>
-      <c r="T128" s="40"/>
-      <c r="U128" s="41"/>
+        <v>40</v>
+      </c>
+      <c r="D128" s="72"/>
+      <c r="E128" s="73"/>
+      <c r="F128" s="73"/>
+      <c r="G128" s="73"/>
+      <c r="H128" s="73"/>
+      <c r="I128" s="73"/>
+      <c r="J128" s="73"/>
+      <c r="K128" s="73"/>
+      <c r="L128" s="73"/>
+      <c r="M128" s="73"/>
+      <c r="N128" s="73"/>
+      <c r="O128" s="73"/>
+      <c r="P128" s="73"/>
+      <c r="Q128" s="73"/>
+      <c r="R128" s="73"/>
+      <c r="S128" s="73"/>
+      <c r="T128" s="73"/>
+      <c r="U128" s="74"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="50"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="31" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D129" s="39"/>
-      <c r="E129" s="40"/>
-      <c r="F129" s="40"/>
-      <c r="G129" s="40"/>
-      <c r="H129" s="40"/>
-      <c r="I129" s="40"/>
-      <c r="J129" s="40"/>
-      <c r="K129" s="40"/>
-      <c r="L129" s="40"/>
-      <c r="M129" s="40"/>
-      <c r="N129" s="40"/>
-      <c r="O129" s="40"/>
-      <c r="P129" s="40"/>
-      <c r="Q129" s="40"/>
-      <c r="R129" s="40"/>
-      <c r="S129" s="40"/>
-      <c r="T129" s="40"/>
-      <c r="U129" s="41"/>
+        <v>44</v>
+      </c>
+      <c r="D129" s="72"/>
+      <c r="E129" s="73"/>
+      <c r="F129" s="73"/>
+      <c r="G129" s="73"/>
+      <c r="H129" s="73"/>
+      <c r="I129" s="73"/>
+      <c r="J129" s="73"/>
+      <c r="K129" s="73"/>
+      <c r="L129" s="73"/>
+      <c r="M129" s="73"/>
+      <c r="N129" s="73"/>
+      <c r="O129" s="73"/>
+      <c r="P129" s="73"/>
+      <c r="Q129" s="73"/>
+      <c r="R129" s="73"/>
+      <c r="S129" s="73"/>
+      <c r="T129" s="73"/>
+      <c r="U129" s="74"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="45">
+      <c r="A130" s="57">
         <v>19</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="39"/>
-      <c r="E130" s="40"/>
-      <c r="F130" s="40"/>
-      <c r="G130" s="40"/>
-      <c r="H130" s="40"/>
-      <c r="I130" s="40"/>
-      <c r="J130" s="40"/>
-      <c r="K130" s="40"/>
-      <c r="L130" s="40"/>
-      <c r="M130" s="40"/>
-      <c r="N130" s="40"/>
-      <c r="O130" s="40"/>
-      <c r="P130" s="40"/>
-      <c r="Q130" s="40"/>
-      <c r="R130" s="40"/>
-      <c r="S130" s="40"/>
-      <c r="T130" s="40"/>
-      <c r="U130" s="41"/>
+      <c r="D130" s="72"/>
+      <c r="E130" s="73"/>
+      <c r="F130" s="73"/>
+      <c r="G130" s="73"/>
+      <c r="H130" s="73"/>
+      <c r="I130" s="73"/>
+      <c r="J130" s="73"/>
+      <c r="K130" s="73"/>
+      <c r="L130" s="73"/>
+      <c r="M130" s="73"/>
+      <c r="N130" s="73"/>
+      <c r="O130" s="73"/>
+      <c r="P130" s="73"/>
+      <c r="Q130" s="73"/>
+      <c r="R130" s="73"/>
+      <c r="S130" s="73"/>
+      <c r="T130" s="73"/>
+      <c r="U130" s="74"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="46"/>
+      <c r="A131" s="58"/>
       <c r="B131" s="33" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="39"/>
-      <c r="E131" s="40"/>
-      <c r="F131" s="40"/>
-      <c r="G131" s="40"/>
-      <c r="H131" s="40"/>
-      <c r="I131" s="40"/>
-      <c r="J131" s="40"/>
-      <c r="K131" s="40"/>
-      <c r="L131" s="40"/>
-      <c r="M131" s="40"/>
-      <c r="N131" s="40"/>
-      <c r="O131" s="40"/>
-      <c r="P131" s="40"/>
-      <c r="Q131" s="40"/>
-      <c r="R131" s="40"/>
-      <c r="S131" s="40"/>
-      <c r="T131" s="40"/>
-      <c r="U131" s="41"/>
+      <c r="D131" s="72"/>
+      <c r="E131" s="73"/>
+      <c r="F131" s="73"/>
+      <c r="G131" s="73"/>
+      <c r="H131" s="73"/>
+      <c r="I131" s="73"/>
+      <c r="J131" s="73"/>
+      <c r="K131" s="73"/>
+      <c r="L131" s="73"/>
+      <c r="M131" s="73"/>
+      <c r="N131" s="73"/>
+      <c r="O131" s="73"/>
+      <c r="P131" s="73"/>
+      <c r="Q131" s="73"/>
+      <c r="R131" s="73"/>
+      <c r="S131" s="73"/>
+      <c r="T131" s="73"/>
+      <c r="U131" s="74"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="46"/>
+      <c r="A132" s="58"/>
       <c r="B132" s="33" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D132" s="39"/>
-      <c r="E132" s="40"/>
-      <c r="F132" s="40"/>
-      <c r="G132" s="40"/>
-      <c r="H132" s="40"/>
-      <c r="I132" s="40"/>
-      <c r="J132" s="40"/>
-      <c r="K132" s="40"/>
-      <c r="L132" s="40"/>
-      <c r="M132" s="40"/>
-      <c r="N132" s="40"/>
-      <c r="O132" s="40"/>
-      <c r="P132" s="40"/>
-      <c r="Q132" s="40"/>
-      <c r="R132" s="40"/>
-      <c r="S132" s="40"/>
-      <c r="T132" s="40"/>
-      <c r="U132" s="41"/>
+        <v>27</v>
+      </c>
+      <c r="D132" s="72"/>
+      <c r="E132" s="73"/>
+      <c r="F132" s="73"/>
+      <c r="G132" s="73"/>
+      <c r="H132" s="73"/>
+      <c r="I132" s="73"/>
+      <c r="J132" s="73"/>
+      <c r="K132" s="73"/>
+      <c r="L132" s="73"/>
+      <c r="M132" s="73"/>
+      <c r="N132" s="73"/>
+      <c r="O132" s="73"/>
+      <c r="P132" s="73"/>
+      <c r="Q132" s="73"/>
+      <c r="R132" s="73"/>
+      <c r="S132" s="73"/>
+      <c r="T132" s="73"/>
+      <c r="U132" s="74"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="46"/>
+      <c r="A133" s="58"/>
       <c r="B133" s="33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D133" s="39"/>
-      <c r="E133" s="40"/>
-      <c r="F133" s="40"/>
-      <c r="G133" s="40"/>
-      <c r="H133" s="40"/>
-      <c r="I133" s="40"/>
-      <c r="J133" s="40"/>
-      <c r="K133" s="40"/>
-      <c r="L133" s="40"/>
-      <c r="M133" s="40"/>
-      <c r="N133" s="40"/>
-      <c r="O133" s="40"/>
-      <c r="P133" s="40"/>
-      <c r="Q133" s="40"/>
-      <c r="R133" s="40"/>
-      <c r="S133" s="40"/>
-      <c r="T133" s="40"/>
-      <c r="U133" s="41"/>
+        <v>34</v>
+      </c>
+      <c r="D133" s="72"/>
+      <c r="E133" s="73"/>
+      <c r="F133" s="73"/>
+      <c r="G133" s="73"/>
+      <c r="H133" s="73"/>
+      <c r="I133" s="73"/>
+      <c r="J133" s="73"/>
+      <c r="K133" s="73"/>
+      <c r="L133" s="73"/>
+      <c r="M133" s="73"/>
+      <c r="N133" s="73"/>
+      <c r="O133" s="73"/>
+      <c r="P133" s="73"/>
+      <c r="Q133" s="73"/>
+      <c r="R133" s="73"/>
+      <c r="S133" s="73"/>
+      <c r="T133" s="73"/>
+      <c r="U133" s="74"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="46"/>
+      <c r="A134" s="58"/>
       <c r="B134" s="33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D134" s="39"/>
-      <c r="E134" s="40"/>
-      <c r="F134" s="40"/>
-      <c r="G134" s="40"/>
-      <c r="H134" s="40"/>
-      <c r="I134" s="40"/>
-      <c r="J134" s="40"/>
-      <c r="K134" s="40"/>
-      <c r="L134" s="40"/>
-      <c r="M134" s="40"/>
-      <c r="N134" s="40"/>
-      <c r="O134" s="40"/>
-      <c r="P134" s="40"/>
-      <c r="Q134" s="40"/>
-      <c r="R134" s="40"/>
-      <c r="S134" s="40"/>
-      <c r="T134" s="40"/>
-      <c r="U134" s="41"/>
+        <v>37</v>
+      </c>
+      <c r="D134" s="72"/>
+      <c r="E134" s="73"/>
+      <c r="F134" s="73"/>
+      <c r="G134" s="73"/>
+      <c r="H134" s="73"/>
+      <c r="I134" s="73"/>
+      <c r="J134" s="73"/>
+      <c r="K134" s="73"/>
+      <c r="L134" s="73"/>
+      <c r="M134" s="73"/>
+      <c r="N134" s="73"/>
+      <c r="O134" s="73"/>
+      <c r="P134" s="73"/>
+      <c r="Q134" s="73"/>
+      <c r="R134" s="73"/>
+      <c r="S134" s="73"/>
+      <c r="T134" s="73"/>
+      <c r="U134" s="74"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="46"/>
+      <c r="A135" s="58"/>
       <c r="B135" s="33" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D135" s="39"/>
-      <c r="E135" s="40"/>
-      <c r="F135" s="40"/>
-      <c r="G135" s="40"/>
-      <c r="H135" s="40"/>
-      <c r="I135" s="40"/>
-      <c r="J135" s="40"/>
-      <c r="K135" s="40"/>
-      <c r="L135" s="40"/>
-      <c r="M135" s="40"/>
-      <c r="N135" s="40"/>
-      <c r="O135" s="40"/>
-      <c r="P135" s="40"/>
-      <c r="Q135" s="40"/>
-      <c r="R135" s="40"/>
-      <c r="S135" s="40"/>
-      <c r="T135" s="40"/>
-      <c r="U135" s="41"/>
+        <v>40</v>
+      </c>
+      <c r="D135" s="72"/>
+      <c r="E135" s="73"/>
+      <c r="F135" s="73"/>
+      <c r="G135" s="73"/>
+      <c r="H135" s="73"/>
+      <c r="I135" s="73"/>
+      <c r="J135" s="73"/>
+      <c r="K135" s="73"/>
+      <c r="L135" s="73"/>
+      <c r="M135" s="73"/>
+      <c r="N135" s="73"/>
+      <c r="O135" s="73"/>
+      <c r="P135" s="73"/>
+      <c r="Q135" s="73"/>
+      <c r="R135" s="73"/>
+      <c r="S135" s="73"/>
+      <c r="T135" s="73"/>
+      <c r="U135" s="74"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="47"/>
+      <c r="A136" s="59"/>
       <c r="B136" s="33" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="D136" s="42"/>
-      <c r="E136" s="43"/>
-      <c r="F136" s="43"/>
-      <c r="G136" s="43"/>
-      <c r="H136" s="43"/>
-      <c r="I136" s="43"/>
-      <c r="J136" s="43"/>
-      <c r="K136" s="43"/>
-      <c r="L136" s="43"/>
-      <c r="M136" s="43"/>
-      <c r="N136" s="43"/>
-      <c r="O136" s="43"/>
-      <c r="P136" s="43"/>
-      <c r="Q136" s="43"/>
-      <c r="R136" s="43"/>
-      <c r="S136" s="43"/>
-      <c r="T136" s="43"/>
-      <c r="U136" s="44"/>
+        <v>44</v>
+      </c>
+      <c r="D136" s="75"/>
+      <c r="E136" s="76"/>
+      <c r="F136" s="76"/>
+      <c r="G136" s="76"/>
+      <c r="H136" s="76"/>
+      <c r="I136" s="76"/>
+      <c r="J136" s="76"/>
+      <c r="K136" s="76"/>
+      <c r="L136" s="76"/>
+      <c r="M136" s="76"/>
+      <c r="N136" s="76"/>
+      <c r="O136" s="76"/>
+      <c r="P136" s="76"/>
+      <c r="Q136" s="76"/>
+      <c r="R136" s="76"/>
+      <c r="S136" s="76"/>
+      <c r="T136" s="76"/>
+      <c r="U136" s="77"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6709,6 +6754,26 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6725,26 +6790,6 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/raw/Timetable_2026Autumn_2026LE.xlsx
+++ b/raw/Timetable_2026Autumn_2026LE.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="113" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB6C925B-8A5C-4289-9B6A-B6EC4E62E320}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8595E935-3E0A-40B2-A3F8-EDBF2874122D}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="189">
   <si>
     <t>week</t>
   </si>
@@ -152,9 +152,6 @@
     <t>Fri</t>
   </si>
   <si>
-    <t>C303</t>
-  </si>
-  <si>
     <t>5       Sep.</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>14       Nov.</t>
+  </si>
+  <si>
+    <t>Presentation</t>
   </si>
   <si>
     <t>15       Nov.</t>
@@ -944,7 +944,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1078,6 +1078,61 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1114,24 +1169,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1150,40 +1187,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1529,81 +1535,81 @@
   <sheetData>
     <row r="1" spans="1:27"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="78" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="66"/>
-      <c r="D2" s="45" t="s">
+      <c r="C2" s="79"/>
+      <c r="D2" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="45" t="s">
+      <c r="E2" s="65"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="45" t="s">
+      <c r="H2" s="65"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="46"/>
-      <c r="L2" s="47"/>
-      <c r="M2" s="45" t="s">
+      <c r="K2" s="65"/>
+      <c r="L2" s="66"/>
+      <c r="M2" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="46"/>
-      <c r="O2" s="47"/>
-      <c r="P2" s="45" t="s">
+      <c r="N2" s="65"/>
+      <c r="O2" s="66"/>
+      <c r="P2" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="46"/>
-      <c r="R2" s="47"/>
-      <c r="S2" s="45" t="s">
+      <c r="Q2" s="65"/>
+      <c r="R2" s="66"/>
+      <c r="S2" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="46"/>
-      <c r="U2" s="47"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="66"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="45" t="s">
+      <c r="A3" s="77"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="46"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="45" t="s">
+      <c r="E3" s="65"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="45" t="s">
+      <c r="H3" s="65"/>
+      <c r="I3" s="66"/>
+      <c r="J3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="46"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="45" t="s">
+      <c r="K3" s="65"/>
+      <c r="L3" s="66"/>
+      <c r="M3" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="46"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="45" t="s">
+      <c r="N3" s="65"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="46"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="45" t="s">
+      <c r="Q3" s="65"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="46"/>
-      <c r="U3" s="47"/>
+      <c r="T3" s="65"/>
+      <c r="U3" s="66"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="57">
+      <c r="A4" s="58">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1657,7 +1663,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="58"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -1705,7 +1711,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="58"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="6" t="s">
         <v>26</v>
       </c>
@@ -1765,7 +1771,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="58"/>
+      <c r="A7" s="59"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -1811,7 +1817,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="58"/>
+      <c r="A8" s="59"/>
       <c r="B8" s="6" t="s">
         <v>36</v>
       </c>
@@ -1825,7 +1831,7 @@
         <v>29</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>28</v>
@@ -1834,7 +1840,7 @@
         <v>29</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="8"/>
@@ -1869,30 +1875,30 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="58"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="E9" s="8"/>
       <c r="F9" s="9"/>
       <c r="G9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H9" s="8"/>
       <c r="I9" s="9"/>
       <c r="J9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="8"/>
       <c r="L9" s="9"/>
       <c r="M9" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N9" s="8"/>
       <c r="O9" s="9"/>
@@ -1903,7 +1909,7 @@
       <c r="T9" s="8"/>
       <c r="U9" s="9"/>
       <c r="W9" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X9" s="7"/>
       <c r="Y9" s="7">
@@ -1919,12 +1925,12 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="59"/>
+      <c r="A10" s="60"/>
       <c r="B10" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>44</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="8"/>
@@ -1945,10 +1951,10 @@
       <c r="T10" s="8"/>
       <c r="U10" s="9"/>
       <c r="W10" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="X10" s="10" t="s">
         <v>45</v>
-      </c>
-      <c r="X10" s="10" t="s">
-        <v>46</v>
       </c>
       <c r="Y10" s="7">
         <v>48</v>
@@ -1963,11 +1969,11 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="60">
+      <c r="A11" s="61">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>15</v>
@@ -2007,10 +2013,10 @@
       <c r="T11" s="13"/>
       <c r="U11" s="14"/>
       <c r="W11" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="X11" s="10" t="s">
         <v>48</v>
-      </c>
-      <c r="X11" s="10" t="s">
-        <v>49</v>
       </c>
       <c r="Y11" s="7">
         <v>48</v>
@@ -2025,9 +2031,9 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="61"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>25</v>
@@ -2071,9 +2077,9 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="61"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>27</v>
@@ -2085,7 +2091,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G13" s="11" t="s">
         <v>28</v>
@@ -2094,7 +2100,7 @@
         <v>29</v>
       </c>
       <c r="I13" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J13" s="11" t="s">
         <v>19</v>
@@ -2107,22 +2113,22 @@
       <c r="N13" s="13"/>
       <c r="O13" s="14"/>
       <c r="P13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q13" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="Q13" s="13" t="s">
+      <c r="R13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="R13" s="14" t="s">
-        <v>54</v>
-      </c>
       <c r="S13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T13" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T13" s="13" t="s">
+      <c r="U13" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="U13" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="W13" s="10" t="s">
         <v>19</v>
@@ -2141,9 +2147,9 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="61"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>34</v>
@@ -2177,30 +2183,30 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="61"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J15" s="11"/>
       <c r="K15" s="13"/>
@@ -2218,30 +2224,30 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="61"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
       <c r="G16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14"/>
       <c r="J16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="14"/>
       <c r="M16" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="14"/>
@@ -2253,12 +2259,12 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="62"/>
+      <c r="A17" s="63"/>
       <c r="B17" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="11"/>
       <c r="E17" s="13"/>
@@ -2280,11 +2286,11 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="57">
+      <c r="A18" s="58">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>15</v>
@@ -2325,9 +2331,9 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="58"/>
+      <c r="A19" s="59"/>
       <c r="B19" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>25</v>
@@ -2356,9 +2362,9 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="58"/>
+      <c r="A20" s="59"/>
       <c r="B20" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>27</v>
@@ -2370,7 +2376,7 @@
         <v>29</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>28</v>
@@ -2379,7 +2385,7 @@
         <v>29</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>19</v>
@@ -2392,28 +2398,28 @@
       <c r="N20" s="8"/>
       <c r="O20" s="9"/>
       <c r="P20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="Q20" s="8" t="s">
+      <c r="R20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="R20" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="S20" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T20" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="T20" s="8" t="s">
+      <c r="U20" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="U20" s="9" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="58"/>
+      <c r="A21" s="59"/>
       <c r="B21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>34</v>
@@ -2442,9 +2448,9 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="58"/>
+      <c r="A22" s="59"/>
       <c r="B22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>37</v>
@@ -2456,7 +2462,7 @@
         <v>29</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>28</v>
@@ -2465,7 +2471,7 @@
         <v>29</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J22" s="6"/>
       <c r="K22" s="8"/>
@@ -2483,12 +2489,12 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="58"/>
+      <c r="A23" s="59"/>
       <c r="B23" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="16"/>
@@ -2510,12 +2516,12 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="59"/>
+      <c r="A24" s="60"/>
       <c r="B24" s="18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="20"/>
       <c r="E24" s="21"/>
@@ -2537,11 +2543,11 @@
       <c r="U24" s="24"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="60">
+      <c r="A25" s="61">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C25" s="12" t="s">
         <v>15</v>
@@ -2582,9 +2588,9 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="61"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>25</v>
@@ -2613,9 +2619,9 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="61"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>27</v>
@@ -2627,7 +2633,7 @@
         <v>29</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>28</v>
@@ -2636,7 +2642,7 @@
         <v>29</v>
       </c>
       <c r="I27" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J27" s="11" t="s">
         <v>19</v>
@@ -2649,28 +2655,28 @@
       <c r="N27" s="13"/>
       <c r="O27" s="14"/>
       <c r="P27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="Q27" s="13" t="s">
+      <c r="R27" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="R27" s="14" t="s">
-        <v>54</v>
-      </c>
       <c r="S27" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T27" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T27" s="13" t="s">
+      <c r="U27" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="U27" s="14" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="61"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>34</v>
@@ -2699,94 +2705,94 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="61"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="28" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="68"/>
+      <c r="F29" s="68"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="68"/>
+      <c r="I29" s="68"/>
+      <c r="J29" s="68"/>
+      <c r="K29" s="68"/>
+      <c r="L29" s="68"/>
+      <c r="M29" s="68"/>
+      <c r="N29" s="68"/>
+      <c r="O29" s="68"/>
+      <c r="P29" s="68"/>
+      <c r="Q29" s="68"/>
+      <c r="R29" s="68"/>
+      <c r="S29" s="68"/>
+      <c r="T29" s="68"/>
+      <c r="U29" s="69"/>
+    </row>
+    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="62"/>
+      <c r="B30" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="E29" s="49"/>
-      <c r="F29" s="49"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="49"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="49"/>
-      <c r="L29" s="49"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="49"/>
-      <c r="O29" s="49"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="49"/>
-      <c r="R29" s="49"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="49"/>
-      <c r="U29" s="50"/>
-    </row>
-    <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="61"/>
-      <c r="B30" s="28" t="s">
+      <c r="C30" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="70"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="72"/>
+    </row>
+    <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="63"/>
+      <c r="B31" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="51"/>
-      <c r="E30" s="52"/>
-      <c r="F30" s="52"/>
-      <c r="G30" s="52"/>
-      <c r="H30" s="52"/>
-      <c r="I30" s="52"/>
-      <c r="J30" s="52"/>
-      <c r="K30" s="52"/>
-      <c r="L30" s="52"/>
-      <c r="M30" s="52"/>
-      <c r="N30" s="52"/>
-      <c r="O30" s="52"/>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="52"/>
-      <c r="R30" s="52"/>
-      <c r="S30" s="52"/>
-      <c r="T30" s="52"/>
-      <c r="U30" s="53"/>
-    </row>
-    <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="62"/>
-      <c r="B31" s="28" t="s">
+      <c r="C31" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" s="73"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="74"/>
+      <c r="K31" s="74"/>
+      <c r="L31" s="74"/>
+      <c r="M31" s="74"/>
+      <c r="N31" s="74"/>
+      <c r="O31" s="74"/>
+      <c r="P31" s="74"/>
+      <c r="Q31" s="74"/>
+      <c r="R31" s="74"/>
+      <c r="S31" s="74"/>
+      <c r="T31" s="74"/>
+      <c r="U31" s="75"/>
+    </row>
+    <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="58">
+        <v>5</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="54"/>
-      <c r="E31" s="55"/>
-      <c r="F31" s="55"/>
-      <c r="G31" s="55"/>
-      <c r="H31" s="55"/>
-      <c r="I31" s="55"/>
-      <c r="J31" s="55"/>
-      <c r="K31" s="55"/>
-      <c r="L31" s="55"/>
-      <c r="M31" s="55"/>
-      <c r="N31" s="55"/>
-      <c r="O31" s="55"/>
-      <c r="P31" s="55"/>
-      <c r="Q31" s="55"/>
-      <c r="R31" s="55"/>
-      <c r="S31" s="55"/>
-      <c r="T31" s="55"/>
-      <c r="U31" s="56"/>
-    </row>
-    <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="57">
-        <v>5</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>15</v>
@@ -2827,9 +2833,9 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="58"/>
+      <c r="A33" s="59"/>
       <c r="B33" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>25</v>
@@ -2858,9 +2864,9 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="58"/>
+      <c r="A34" s="59"/>
       <c r="B34" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>27</v>
@@ -2872,7 +2878,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>28</v>
@@ -2881,7 +2887,7 @@
         <v>29</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>19</v>
@@ -2901,202 +2907,202 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="58"/>
+      <c r="A35" s="59"/>
       <c r="B35" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C35" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="48" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35" s="49"/>
-      <c r="F35" s="49"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="49"/>
-      <c r="I35" s="49"/>
-      <c r="J35" s="49"/>
-      <c r="K35" s="49"/>
-      <c r="L35" s="49"/>
-      <c r="M35" s="49"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="49"/>
-      <c r="P35" s="49"/>
-      <c r="Q35" s="49"/>
-      <c r="R35" s="49"/>
-      <c r="S35" s="49"/>
-      <c r="T35" s="49"/>
-      <c r="U35" s="50"/>
+      <c r="D35" s="67" t="s">
+        <v>70</v>
+      </c>
+      <c r="E35" s="68"/>
+      <c r="F35" s="68"/>
+      <c r="G35" s="68"/>
+      <c r="H35" s="68"/>
+      <c r="I35" s="68"/>
+      <c r="J35" s="68"/>
+      <c r="K35" s="68"/>
+      <c r="L35" s="68"/>
+      <c r="M35" s="68"/>
+      <c r="N35" s="68"/>
+      <c r="O35" s="68"/>
+      <c r="P35" s="68"/>
+      <c r="Q35" s="68"/>
+      <c r="R35" s="68"/>
+      <c r="S35" s="68"/>
+      <c r="T35" s="68"/>
+      <c r="U35" s="69"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="58"/>
+      <c r="A36" s="59"/>
       <c r="B36" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C36" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="51"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-      <c r="K36" s="52"/>
-      <c r="L36" s="52"/>
-      <c r="M36" s="52"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="52"/>
-      <c r="P36" s="52"/>
-      <c r="Q36" s="52"/>
-      <c r="R36" s="52"/>
-      <c r="S36" s="52"/>
-      <c r="T36" s="52"/>
-      <c r="U36" s="53"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="71"/>
+      <c r="G36" s="71"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="71"/>
+      <c r="J36" s="71"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="71"/>
+      <c r="M36" s="71"/>
+      <c r="N36" s="71"/>
+      <c r="O36" s="71"/>
+      <c r="P36" s="71"/>
+      <c r="Q36" s="71"/>
+      <c r="R36" s="71"/>
+      <c r="S36" s="71"/>
+      <c r="T36" s="71"/>
+      <c r="U36" s="72"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="58"/>
+      <c r="A37" s="59"/>
       <c r="B37" s="30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="70"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="71"/>
+      <c r="G37" s="71"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="71"/>
+      <c r="J37" s="71"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="71"/>
+      <c r="M37" s="71"/>
+      <c r="N37" s="71"/>
+      <c r="O37" s="71"/>
+      <c r="P37" s="71"/>
+      <c r="Q37" s="71"/>
+      <c r="R37" s="71"/>
+      <c r="S37" s="71"/>
+      <c r="T37" s="71"/>
+      <c r="U37" s="72"/>
+    </row>
+    <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="60"/>
+      <c r="B38" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C37" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="D37" s="51"/>
-      <c r="E37" s="52"/>
-      <c r="F37" s="52"/>
-      <c r="G37" s="52"/>
-      <c r="H37" s="52"/>
-      <c r="I37" s="52"/>
-      <c r="J37" s="52"/>
-      <c r="K37" s="52"/>
-      <c r="L37" s="52"/>
-      <c r="M37" s="52"/>
-      <c r="N37" s="52"/>
-      <c r="O37" s="52"/>
-      <c r="P37" s="52"/>
-      <c r="Q37" s="52"/>
-      <c r="R37" s="52"/>
-      <c r="S37" s="52"/>
-      <c r="T37" s="52"/>
-      <c r="U37" s="53"/>
-    </row>
-    <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="59"/>
-      <c r="B38" s="30" t="s">
+      <c r="C38" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" s="70"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="71"/>
+      <c r="G38" s="71"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="71"/>
+      <c r="J38" s="71"/>
+      <c r="K38" s="71"/>
+      <c r="L38" s="71"/>
+      <c r="M38" s="71"/>
+      <c r="N38" s="71"/>
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="71"/>
+      <c r="R38" s="71"/>
+      <c r="S38" s="71"/>
+      <c r="T38" s="71"/>
+      <c r="U38" s="72"/>
+    </row>
+    <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="61">
+        <v>6</v>
+      </c>
+      <c r="B39" s="30" t="s">
         <v>80</v>
-      </c>
-      <c r="C38" s="29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D38" s="51"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-      <c r="I38" s="52"/>
-      <c r="J38" s="52"/>
-      <c r="K38" s="52"/>
-      <c r="L38" s="52"/>
-      <c r="M38" s="52"/>
-      <c r="N38" s="52"/>
-      <c r="O38" s="52"/>
-      <c r="P38" s="52"/>
-      <c r="Q38" s="52"/>
-      <c r="R38" s="52"/>
-      <c r="S38" s="52"/>
-      <c r="T38" s="52"/>
-      <c r="U38" s="53"/>
-    </row>
-    <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="60">
-        <v>6</v>
-      </c>
-      <c r="B39" s="30" t="s">
-        <v>81</v>
       </c>
       <c r="C39" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
-      <c r="J39" s="52"/>
-      <c r="K39" s="52"/>
-      <c r="L39" s="52"/>
-      <c r="M39" s="52"/>
-      <c r="N39" s="52"/>
-      <c r="O39" s="52"/>
-      <c r="P39" s="52"/>
-      <c r="Q39" s="52"/>
-      <c r="R39" s="52"/>
-      <c r="S39" s="52"/>
-      <c r="T39" s="52"/>
-      <c r="U39" s="53"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="71"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="71"/>
+      <c r="J39" s="71"/>
+      <c r="K39" s="71"/>
+      <c r="L39" s="71"/>
+      <c r="M39" s="71"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="71"/>
+      <c r="P39" s="71"/>
+      <c r="Q39" s="71"/>
+      <c r="R39" s="71"/>
+      <c r="S39" s="71"/>
+      <c r="T39" s="71"/>
+      <c r="U39" s="72"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="61"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C40" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="51"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="52"/>
-      <c r="I40" s="52"/>
-      <c r="J40" s="52"/>
-      <c r="K40" s="52"/>
-      <c r="L40" s="52"/>
-      <c r="M40" s="52"/>
-      <c r="N40" s="52"/>
-      <c r="O40" s="52"/>
-      <c r="P40" s="52"/>
-      <c r="Q40" s="52"/>
-      <c r="R40" s="52"/>
-      <c r="S40" s="52"/>
-      <c r="T40" s="52"/>
-      <c r="U40" s="53"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="71"/>
+      <c r="G40" s="71"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
+      <c r="J40" s="71"/>
+      <c r="K40" s="71"/>
+      <c r="L40" s="71"/>
+      <c r="M40" s="71"/>
+      <c r="N40" s="71"/>
+      <c r="O40" s="71"/>
+      <c r="P40" s="71"/>
+      <c r="Q40" s="71"/>
+      <c r="R40" s="71"/>
+      <c r="S40" s="71"/>
+      <c r="T40" s="71"/>
+      <c r="U40" s="72"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="61"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="D41" s="54"/>
-      <c r="E41" s="55"/>
-      <c r="F41" s="55"/>
-      <c r="G41" s="55"/>
-      <c r="H41" s="55"/>
-      <c r="I41" s="55"/>
-      <c r="J41" s="55"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="55"/>
-      <c r="M41" s="55"/>
-      <c r="N41" s="55"/>
-      <c r="O41" s="55"/>
-      <c r="P41" s="55"/>
-      <c r="Q41" s="55"/>
-      <c r="R41" s="55"/>
-      <c r="S41" s="55"/>
-      <c r="T41" s="55"/>
-      <c r="U41" s="56"/>
+      <c r="D41" s="73"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="74"/>
+      <c r="K41" s="74"/>
+      <c r="L41" s="74"/>
+      <c r="M41" s="74"/>
+      <c r="N41" s="74"/>
+      <c r="O41" s="74"/>
+      <c r="P41" s="74"/>
+      <c r="Q41" s="74"/>
+      <c r="R41" s="74"/>
+      <c r="S41" s="74"/>
+      <c r="T41" s="74"/>
+      <c r="U41" s="75"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="61"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>34</v>
@@ -3125,9 +3131,9 @@
       <c r="U42" s="14"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="61"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="31" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>37</v>
@@ -3154,12 +3160,12 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="61"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D44" s="18"/>
       <c r="E44" s="23"/>
@@ -3181,12 +3187,12 @@
       <c r="U44" s="24"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="62"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="31" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D45" s="11"/>
       <c r="E45" s="13"/>
@@ -3208,11 +3214,11 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="57">
+      <c r="A46" s="58">
         <v>7</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
@@ -3253,9 +3259,9 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="58"/>
+      <c r="A47" s="59"/>
       <c r="B47" s="33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>25</v>
@@ -3274,19 +3280,19 @@
         <v>31</v>
       </c>
       <c r="K47" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L47" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="L47" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>31</v>
       </c>
       <c r="N47" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O47" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="O47" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="8"/>
@@ -3296,9 +3302,9 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="58"/>
+      <c r="A48" s="59"/>
       <c r="B48" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>27</v>
@@ -3310,7 +3316,7 @@
         <v>29</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>28</v>
@@ -3319,7 +3325,7 @@
         <v>29</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>19</v>
@@ -3339,9 +3345,9 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="58"/>
+      <c r="A49" s="59"/>
       <c r="B49" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>34</v>
@@ -3360,19 +3366,19 @@
         <v>31</v>
       </c>
       <c r="K49" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L49" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="L49" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>31</v>
       </c>
       <c r="N49" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O49" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="O49" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="8"/>
@@ -3382,30 +3388,30 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="58"/>
+      <c r="A50" s="59"/>
       <c r="B50" s="33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>37</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E50" s="8" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H50" s="8" t="s">
         <v>29</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="8"/>
@@ -3423,30 +3429,30 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="58"/>
+      <c r="A51" s="59"/>
       <c r="B51" s="33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C51" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="E51" s="8"/>
       <c r="F51" s="9"/>
       <c r="G51" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H51" s="8"/>
       <c r="I51" s="9"/>
       <c r="J51" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K51" s="8"/>
       <c r="L51" s="9"/>
       <c r="M51" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N51" s="8"/>
       <c r="O51" s="9"/>
@@ -3458,12 +3464,12 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="59"/>
+      <c r="A52" s="60"/>
       <c r="B52" s="33" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="8"/>
@@ -3485,11 +3491,11 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="60">
+      <c r="A53" s="61">
         <v>8</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>15</v>
@@ -3530,9 +3536,9 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="61"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="31" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>25</v>
@@ -3548,22 +3554,22 @@
       <c r="H54" s="13"/>
       <c r="I54" s="14"/>
       <c r="J54" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K54" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K54" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L54" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M54" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N54" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N54" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O54" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P54" s="11"/>
       <c r="Q54" s="13"/>
@@ -3573,9 +3579,9 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="61"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="31" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>27</v>
@@ -3587,7 +3593,7 @@
         <v>29</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G55" s="11" t="s">
         <v>28</v>
@@ -3596,7 +3602,7 @@
         <v>29</v>
       </c>
       <c r="I55" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J55" s="11" t="s">
         <v>19</v>
@@ -3609,28 +3615,28 @@
       <c r="N55" s="13"/>
       <c r="O55" s="14"/>
       <c r="P55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q55" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="Q55" s="13" t="s">
+      <c r="R55" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="R55" s="14" t="s">
-        <v>54</v>
-      </c>
       <c r="S55" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T55" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="T55" s="13" t="s">
+      <c r="U55" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="U55" s="14" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="61"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="31" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>34</v>
@@ -3646,22 +3652,22 @@
       <c r="H56" s="13"/>
       <c r="I56" s="14"/>
       <c r="J56" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K56" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K56" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L56" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M56" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N56" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N56" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O56" s="14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="P56" s="11"/>
       <c r="Q56" s="13"/>
@@ -3671,30 +3677,30 @@
       <c r="U56" s="14"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="61"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C57" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E57" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H57" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I57" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="J57" s="11" t="s">
         <v>20</v>
@@ -3714,30 +3720,30 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="61"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C58" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D58" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="E58" s="13"/>
       <c r="F58" s="14"/>
       <c r="G58" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="14"/>
       <c r="J58" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K58" s="13"/>
       <c r="L58" s="14"/>
       <c r="M58" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N58" s="13"/>
       <c r="O58" s="14"/>
@@ -3749,12 +3755,12 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="62"/>
+      <c r="A59" s="63"/>
       <c r="B59" s="31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D59" s="11"/>
       <c r="E59" s="13"/>
@@ -3776,11 +3782,11 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="57">
+      <c r="A60" s="58">
         <v>9</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
@@ -3821,9 +3827,9 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="58"/>
+      <c r="A61" s="59"/>
       <c r="B61" s="33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>25</v>
@@ -3842,19 +3848,19 @@
         <v>31</v>
       </c>
       <c r="K61" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L61" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="L61" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>31</v>
       </c>
       <c r="N61" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O61" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="O61" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="8"/>
@@ -3864,9 +3870,9 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="58"/>
+      <c r="A62" s="59"/>
       <c r="B62" s="33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>27</v>
@@ -3878,7 +3884,7 @@
         <v>29</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>28</v>
@@ -3887,7 +3893,7 @@
         <v>29</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>19</v>
@@ -3900,28 +3906,28 @@
       <c r="N62" s="8"/>
       <c r="O62" s="9"/>
       <c r="P62" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q62" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="Q62" s="8" t="s">
+      <c r="R62" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="R62" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="S62" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T62" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="T62" s="8" t="s">
+      <c r="U62" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="U62" s="9" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="58"/>
+      <c r="A63" s="59"/>
       <c r="B63" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>34</v>
@@ -3940,19 +3946,19 @@
         <v>35</v>
       </c>
       <c r="K63" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L63" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="L63" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>35</v>
       </c>
       <c r="N63" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="O63" s="9" t="s">
         <v>90</v>
-      </c>
-      <c r="O63" s="9" t="s">
-        <v>91</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="8"/>
@@ -3962,9 +3968,9 @@
       <c r="U63" s="34"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="58"/>
+      <c r="A64" s="59"/>
       <c r="B64" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>37</v>
@@ -3976,7 +3982,7 @@
         <v>29</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>28</v>
@@ -3985,7 +3991,7 @@
         <v>29</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>20</v>
@@ -4005,30 +4011,30 @@
       <c r="U64" s="34"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="58"/>
+      <c r="A65" s="59"/>
       <c r="B65" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D65" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="E65" s="8"/>
       <c r="F65" s="9"/>
       <c r="G65" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H65" s="8"/>
       <c r="I65" s="9"/>
       <c r="J65" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K65" s="8"/>
       <c r="L65" s="9"/>
       <c r="M65" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N65" s="8"/>
       <c r="O65" s="9"/>
@@ -4040,12 +4046,12 @@
       <c r="U65" s="34"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="59"/>
+      <c r="A66" s="60"/>
       <c r="B66" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="8"/>
@@ -4067,11 +4073,11 @@
       <c r="U66" s="34"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="60">
+      <c r="A67" s="61">
         <v>10</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>15</v>
@@ -4112,9 +4118,9 @@
       <c r="U67" s="35"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="61"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>25</v>
@@ -4130,22 +4136,22 @@
       <c r="H68" s="13"/>
       <c r="I68" s="14"/>
       <c r="J68" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K68" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K68" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L68" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M68" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N68" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N68" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O68" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P68" s="11"/>
       <c r="Q68" s="13"/>
@@ -4155,9 +4161,9 @@
       <c r="U68" s="35"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="61"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="31" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>27</v>
@@ -4166,19 +4172,19 @@
         <v>31</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G69" s="11" t="s">
         <v>31</v>
       </c>
       <c r="H69" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I69" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J69" s="11" t="s">
         <v>19</v>
@@ -4198,9 +4204,9 @@
       <c r="U69" s="35"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="61"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C70" s="12" t="s">
         <v>34</v>
@@ -4216,22 +4222,22 @@
       <c r="H70" s="13"/>
       <c r="I70" s="14"/>
       <c r="J70" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K70" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K70" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L70" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M70" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N70" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N70" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O70" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P70" s="11"/>
       <c r="Q70" s="13"/>
@@ -4241,30 +4247,30 @@
       <c r="U70" s="35"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="61"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E71" s="13" t="s">
         <v>29</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H71" s="13" t="s">
         <v>29</v>
       </c>
       <c r="I71" s="14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="J71" s="11" t="s">
         <v>20</v>
@@ -4284,12 +4290,12 @@
       <c r="U71" s="35"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="61"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="31" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D72" s="11"/>
       <c r="E72" s="13"/>
@@ -4311,12 +4317,12 @@
       <c r="U72" s="35"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="62"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D73" s="11"/>
       <c r="E73" s="13"/>
@@ -4338,11 +4344,11 @@
       <c r="U73" s="35"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="57">
+      <c r="A74" s="58">
         <v>11</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -4383,9 +4389,9 @@
       <c r="U74" s="34"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="58"/>
+      <c r="A75" s="59"/>
       <c r="B75" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>25</v>
@@ -4401,22 +4407,22 @@
       <c r="H75" s="8"/>
       <c r="I75" s="9"/>
       <c r="J75" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K75" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K75" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L75" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M75" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N75" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N75" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O75" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="8"/>
@@ -4426,9 +4432,9 @@
       <c r="U75" s="34"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="58"/>
+      <c r="A76" s="59"/>
       <c r="B76" s="33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>27</v>
@@ -4437,19 +4443,19 @@
         <v>31</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>31</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I76" s="79" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I76" s="45" t="s">
+        <v>116</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>19</v>
@@ -4462,28 +4468,28 @@
       <c r="N76" s="8"/>
       <c r="O76" s="9"/>
       <c r="P76" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q76" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="Q76" s="8" t="s">
+      <c r="R76" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="R76" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="S76" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="T76" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="T76" s="8" t="s">
+      <c r="U76" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="U76" s="9" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="58"/>
+      <c r="A77" s="59"/>
       <c r="B77" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>34</v>
@@ -4499,22 +4505,22 @@
       <c r="H77" s="8"/>
       <c r="I77" s="9"/>
       <c r="J77" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K77" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K77" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L77" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M77" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N77" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N77" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O77" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="8"/>
@@ -4524,9 +4530,9 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="58"/>
+      <c r="A78" s="59"/>
       <c r="B78" s="33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>37</v>
@@ -4535,19 +4541,19 @@
         <v>31</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F78" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>31</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I78" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>20</v>
@@ -4567,19 +4573,31 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="58"/>
+      <c r="A79" s="59"/>
       <c r="B79" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D79" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="C79" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D79" s="6"/>
-      <c r="E79" s="8"/>
-      <c r="F79" s="9"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="8"/>
-      <c r="I79" s="9"/>
+      <c r="E79" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="F79" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G79" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="I79" s="48" t="s">
+        <v>30</v>
+      </c>
       <c r="J79" s="6"/>
       <c r="K79" s="8"/>
       <c r="L79" s="9"/>
@@ -4594,12 +4612,12 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="59"/>
+      <c r="A80" s="60"/>
       <c r="B80" s="33" t="s">
         <v>128</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D80" s="6"/>
       <c r="E80" s="8"/>
@@ -4621,7 +4639,7 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="60">
+      <c r="A81" s="61">
         <v>12</v>
       </c>
       <c r="B81" s="31" t="s">
@@ -4666,7 +4684,7 @@
       <c r="U81" s="14"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="61"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="31" t="s">
         <v>130</v>
       </c>
@@ -4684,22 +4702,22 @@
       <c r="H82" s="39"/>
       <c r="I82" s="40"/>
       <c r="J82" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K82" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K82" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L82" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M82" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N82" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N82" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O82" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P82" s="11"/>
       <c r="Q82" s="13"/>
@@ -4709,7 +4727,7 @@
       <c r="U82" s="14"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="61"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="31" t="s">
         <v>131</v>
       </c>
@@ -4720,19 +4738,19 @@
         <v>35</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G83" s="11" t="s">
         <v>35</v>
       </c>
       <c r="H83" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I83" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J83" s="13" t="s">
         <v>19</v>
@@ -4751,7 +4769,7 @@
         <v>133</v>
       </c>
       <c r="R83" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S83" s="11" t="s">
         <v>132</v>
@@ -4760,11 +4778,11 @@
         <v>133</v>
       </c>
       <c r="U83" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="61"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="31" t="s">
         <v>134</v>
       </c>
@@ -4782,22 +4800,22 @@
       <c r="H84" s="36"/>
       <c r="I84" s="14"/>
       <c r="J84" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K84" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="K84" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="L84" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M84" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="N84" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="N84" s="13" t="s">
-        <v>49</v>
-      </c>
       <c r="O84" s="14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P84" s="11"/>
       <c r="Q84" s="13"/>
@@ -4807,7 +4825,7 @@
       <c r="U84" s="14"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="61"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="31" t="s">
         <v>135</v>
       </c>
@@ -4818,19 +4836,19 @@
         <v>31</v>
       </c>
       <c r="E85" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G85" s="41" t="s">
         <v>31</v>
       </c>
       <c r="H85" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I85" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J85" s="13" t="s">
         <v>20</v>
@@ -4850,30 +4868,30 @@
       <c r="U85" s="14"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="61"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="31" t="s">
         <v>136</v>
       </c>
       <c r="C86" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D86" s="25" t="s">
         <v>40</v>
-      </c>
-      <c r="D86" s="25" t="s">
-        <v>41</v>
       </c>
       <c r="E86" s="26"/>
       <c r="F86" s="27"/>
       <c r="G86" s="25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H86" s="26"/>
       <c r="I86" s="27"/>
       <c r="J86" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K86" s="13"/>
       <c r="L86" s="14"/>
       <c r="M86" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N86" s="13"/>
       <c r="O86" s="14"/>
@@ -4885,12 +4903,12 @@
       <c r="U86" s="14"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="62"/>
+      <c r="A87" s="63"/>
       <c r="B87" s="31" t="s">
         <v>137</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D87" s="11"/>
       <c r="E87" s="13"/>
@@ -4912,7 +4930,7 @@
       <c r="U87" s="14"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="57">
+      <c r="A88" s="58">
         <v>13</v>
       </c>
       <c r="B88" s="33" t="s">
@@ -4957,7 +4975,7 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="58"/>
+      <c r="A89" s="59"/>
       <c r="B89" s="33" t="s">
         <v>139</v>
       </c>
@@ -4975,22 +4993,22 @@
       <c r="H89" s="8"/>
       <c r="I89" s="9"/>
       <c r="J89" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K89" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K89" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L89" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M89" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N89" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N89" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O89" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="8"/>
@@ -5000,7 +5018,7 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="58"/>
+      <c r="A90" s="59"/>
       <c r="B90" s="33" t="s">
         <v>140</v>
       </c>
@@ -5011,19 +5029,19 @@
         <v>31</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F90" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>31</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I90" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>19</v>
@@ -5042,7 +5060,7 @@
         <v>133</v>
       </c>
       <c r="R90" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S90" s="6" t="s">
         <v>132</v>
@@ -5051,11 +5069,11 @@
         <v>133</v>
       </c>
       <c r="U90" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="58"/>
+      <c r="A91" s="59"/>
       <c r="B91" s="33" t="s">
         <v>141</v>
       </c>
@@ -5073,22 +5091,22 @@
       <c r="H91" s="8"/>
       <c r="I91" s="9"/>
       <c r="J91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K91" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K91" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L91" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N91" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N91" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O91" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P91" s="6"/>
       <c r="Q91" s="8"/>
@@ -5098,7 +5116,7 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="58"/>
+      <c r="A92" s="59"/>
       <c r="B92" s="33" t="s">
         <v>142</v>
       </c>
@@ -5109,19 +5127,19 @@
         <v>31</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F92" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>31</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I92" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>20</v>
@@ -5141,30 +5159,30 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="58"/>
+      <c r="A93" s="59"/>
       <c r="B93" s="33" t="s">
         <v>143</v>
       </c>
       <c r="C93" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="E93" s="8"/>
       <c r="F93" s="9"/>
       <c r="G93" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H93" s="8"/>
       <c r="I93" s="9"/>
       <c r="J93" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K93" s="8"/>
       <c r="L93" s="9"/>
       <c r="M93" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N93" s="8"/>
       <c r="O93" s="9"/>
@@ -5176,12 +5194,12 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="59"/>
+      <c r="A94" s="60"/>
       <c r="B94" s="33" t="s">
         <v>144</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D94" s="6"/>
       <c r="E94" s="8"/>
@@ -5203,7 +5221,7 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="60">
+      <c r="A95" s="61">
         <v>14</v>
       </c>
       <c r="B95" s="31" t="s">
@@ -5248,7 +5266,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="61"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="31" t="s">
         <v>146</v>
       </c>
@@ -5269,16 +5287,16 @@
         <v>31</v>
       </c>
       <c r="K96" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L96" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M96" s="11" t="s">
         <v>31</v>
       </c>
       <c r="N96" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O96" s="43"/>
       <c r="P96" s="11"/>
@@ -5289,7 +5307,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="61"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="31" t="s">
         <v>147</v>
       </c>
@@ -5297,19 +5315,19 @@
         <v>27</v>
       </c>
       <c r="D97" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E97" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E97" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="F97" s="14" t="s">
         <v>148</v>
       </c>
       <c r="G97" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H97" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I97" s="14" t="s">
         <v>148</v>
@@ -5331,7 +5349,7 @@
         <v>133</v>
       </c>
       <c r="R97" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S97" s="11" t="s">
         <v>132</v>
@@ -5340,11 +5358,11 @@
         <v>133</v>
       </c>
       <c r="U97" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="61"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="31" t="s">
         <v>149</v>
       </c>
@@ -5365,16 +5383,16 @@
         <v>31</v>
       </c>
       <c r="K98" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L98" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M98" s="41" t="s">
         <v>31</v>
       </c>
       <c r="N98" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O98" s="43"/>
       <c r="P98" s="11"/>
@@ -5385,7 +5403,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="61"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="31" t="s">
         <v>150</v>
       </c>
@@ -5393,19 +5411,19 @@
         <v>37</v>
       </c>
       <c r="D99" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E99" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E99" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="F99" s="14" t="s">
         <v>148</v>
       </c>
       <c r="G99" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H99" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I99" s="14" t="s">
         <v>148</v>
@@ -5428,45 +5446,45 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="61"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="31" t="s">
         <v>151</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D100" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E100" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E100" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="F100" s="14" t="s">
         <v>148</v>
       </c>
       <c r="G100" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H100" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H100" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I100" s="14" t="s">
         <v>148</v>
       </c>
       <c r="J100" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K100" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="K100" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="L100" s="14" t="s">
         <v>148</v>
       </c>
       <c r="M100" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N100" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="N100" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="O100" s="14" t="s">
         <v>148</v>
@@ -5479,12 +5497,12 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="62"/>
+      <c r="A101" s="63"/>
       <c r="B101" s="31" t="s">
         <v>152</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D101" s="11"/>
       <c r="E101" s="13"/>
@@ -5506,7 +5524,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="57">
+      <c r="A102" s="58">
         <v>15</v>
       </c>
       <c r="B102" s="33" t="s">
@@ -5551,7 +5569,7 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="58"/>
+      <c r="A103" s="59"/>
       <c r="B103" s="33" t="s">
         <v>154</v>
       </c>
@@ -5569,19 +5587,19 @@
       <c r="H103" s="8"/>
       <c r="I103" s="9"/>
       <c r="J103" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K103" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="K103" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="L103" s="9" t="s">
         <v>148</v>
       </c>
       <c r="M103" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N103" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="N103" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>148</v>
@@ -5594,7 +5612,7 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="58"/>
+      <c r="A104" s="59"/>
       <c r="B104" s="33" t="s">
         <v>155</v>
       </c>
@@ -5602,19 +5620,19 @@
         <v>27</v>
       </c>
       <c r="D104" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E104" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="E104" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="F104" s="9" t="s">
         <v>148</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H104" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="I104" s="9" t="s">
         <v>148</v>
@@ -5636,7 +5654,7 @@
         <v>133</v>
       </c>
       <c r="R104" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S104" s="6" t="s">
         <v>132</v>
@@ -5645,11 +5663,11 @@
         <v>133</v>
       </c>
       <c r="U104" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="58"/>
+      <c r="A105" s="59"/>
       <c r="B105" s="33" t="s">
         <v>156</v>
       </c>
@@ -5667,19 +5685,19 @@
       <c r="H105" s="8"/>
       <c r="I105" s="9"/>
       <c r="J105" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="K105" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="K105" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="L105" s="9" t="s">
         <v>148</v>
       </c>
       <c r="M105" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="N105" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="N105" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>148</v>
@@ -5692,7 +5710,7 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="58"/>
+      <c r="A106" s="59"/>
       <c r="B106" s="33" t="s">
         <v>157</v>
       </c>
@@ -5700,19 +5718,19 @@
         <v>37</v>
       </c>
       <c r="D106" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E106" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="F106" s="9" t="s">
         <v>148</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="H106" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="H106" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="I106" s="9" t="s">
         <v>148</v>
@@ -5735,30 +5753,30 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="58"/>
+      <c r="A107" s="59"/>
       <c r="B107" s="33" t="s">
         <v>158</v>
       </c>
       <c r="C107" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D107" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="E107" s="8"/>
       <c r="F107" s="9"/>
       <c r="G107" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H107" s="8"/>
       <c r="I107" s="9"/>
       <c r="J107" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K107" s="8"/>
       <c r="L107" s="9"/>
       <c r="M107" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N107" s="8"/>
       <c r="O107" s="9"/>
@@ -5770,12 +5788,12 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="59"/>
+      <c r="A108" s="60"/>
       <c r="B108" s="33" t="s">
         <v>159</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D108" s="6"/>
       <c r="E108" s="8"/>
@@ -5797,7 +5815,7 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="60">
+      <c r="A109" s="61">
         <v>16</v>
       </c>
       <c r="B109" s="31" t="s">
@@ -5842,7 +5860,7 @@
       <c r="U109" s="35"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="61"/>
+      <c r="A110" s="62"/>
       <c r="B110" s="31" t="s">
         <v>161</v>
       </c>
@@ -5860,19 +5878,19 @@
       <c r="H110" s="13"/>
       <c r="I110" s="14"/>
       <c r="J110" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K110" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="K110" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="L110" s="14" t="s">
         <v>148</v>
       </c>
       <c r="M110" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N110" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="N110" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="O110" s="14" t="s">
         <v>148</v>
@@ -5885,7 +5903,7 @@
       <c r="U110" s="35"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="61"/>
+      <c r="A111" s="62"/>
       <c r="B111" s="31" t="s">
         <v>162</v>
       </c>
@@ -5893,19 +5911,19 @@
         <v>27</v>
       </c>
       <c r="D111" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E111" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E111" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="F111" s="14" t="s">
         <v>148</v>
       </c>
       <c r="G111" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H111" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H111" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I111" s="14" t="s">
         <v>148</v>
@@ -5927,7 +5945,7 @@
         <v>133</v>
       </c>
       <c r="R111" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S111" s="11" t="s">
         <v>132</v>
@@ -5936,11 +5954,11 @@
         <v>133</v>
       </c>
       <c r="U111" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="61"/>
+      <c r="A112" s="62"/>
       <c r="B112" s="31" t="s">
         <v>163</v>
       </c>
@@ -5958,19 +5976,19 @@
       <c r="H112" s="13"/>
       <c r="I112" s="14"/>
       <c r="J112" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="K112" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="K112" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="L112" s="14" t="s">
         <v>148</v>
       </c>
       <c r="M112" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="N112" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="N112" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="O112" s="14" t="s">
         <v>148</v>
@@ -5983,7 +6001,7 @@
       <c r="U112" s="35"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="61"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="31" t="s">
         <v>164</v>
       </c>
@@ -5991,19 +6009,19 @@
         <v>37</v>
       </c>
       <c r="D113" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E113" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="E113" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="F113" s="14" t="s">
         <v>148</v>
       </c>
       <c r="G113" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H113" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="H113" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="I113" s="14" t="s">
         <v>148</v>
@@ -6026,12 +6044,12 @@
       <c r="U113" s="35"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="61"/>
+      <c r="A114" s="62"/>
       <c r="B114" s="31" t="s">
         <v>165</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D114" s="11"/>
       <c r="E114" s="13"/>
@@ -6053,12 +6071,12 @@
       <c r="U114" s="35"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="62"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="31" t="s">
         <v>166</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D115" s="11"/>
       <c r="E115" s="13"/>
@@ -6080,7 +6098,7 @@
       <c r="U115" s="35"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="57">
+      <c r="A116" s="58">
         <v>17</v>
       </c>
       <c r="B116" s="33" t="s">
@@ -6123,7 +6141,7 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="58"/>
+      <c r="A117" s="59"/>
       <c r="B117" s="33" t="s">
         <v>168</v>
       </c>
@@ -6139,22 +6157,22 @@
       <c r="H117" s="8"/>
       <c r="I117" s="9"/>
       <c r="J117" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K117" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K117" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L117" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M117" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N117" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N117" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O117" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P117" s="6"/>
       <c r="Q117" s="8"/>
@@ -6164,7 +6182,7 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="58"/>
+      <c r="A118" s="59"/>
       <c r="B118" s="33" t="s">
         <v>169</v>
       </c>
@@ -6175,19 +6193,19 @@
         <v>35</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F118" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F118" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I118" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I118" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="8"/>
@@ -6204,7 +6222,7 @@
         <v>133</v>
       </c>
       <c r="R118" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="S118" s="6" t="s">
         <v>132</v>
@@ -6213,11 +6231,11 @@
         <v>133</v>
       </c>
       <c r="U118" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="58"/>
+      <c r="A119" s="59"/>
       <c r="B119" s="33" t="s">
         <v>170</v>
       </c>
@@ -6233,22 +6251,22 @@
       <c r="H119" s="8"/>
       <c r="I119" s="9"/>
       <c r="J119" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K119" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="K119" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="L119" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M119" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="N119" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="N119" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="O119" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P119" s="6"/>
       <c r="Q119" s="8"/>
@@ -6258,7 +6276,7 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="58"/>
+      <c r="A120" s="59"/>
       <c r="B120" s="33" t="s">
         <v>171</v>
       </c>
@@ -6269,19 +6287,19 @@
         <v>35</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="F120" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="F120" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>35</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="I120" s="78" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="I120" s="9" t="s">
+        <v>116</v>
       </c>
       <c r="J120" s="6" t="s">
         <v>20</v>
@@ -6301,12 +6319,12 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="58"/>
+      <c r="A121" s="59"/>
       <c r="B121" s="33" t="s">
         <v>172</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D121" s="6"/>
       <c r="E121" s="8"/>
@@ -6328,12 +6346,12 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="59"/>
+      <c r="A122" s="60"/>
       <c r="B122" s="33" t="s">
         <v>173</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D122" s="6"/>
       <c r="E122" s="8"/>
@@ -6355,7 +6373,7 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="60">
+      <c r="A123" s="61">
         <v>18</v>
       </c>
       <c r="B123" s="31" t="s">
@@ -6364,191 +6382,191 @@
       <c r="C123" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="69" t="s">
+      <c r="D123" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="E123" s="70"/>
-      <c r="F123" s="70"/>
-      <c r="G123" s="70"/>
-      <c r="H123" s="70"/>
-      <c r="I123" s="70"/>
-      <c r="J123" s="70"/>
-      <c r="K123" s="70"/>
-      <c r="L123" s="70"/>
-      <c r="M123" s="70"/>
-      <c r="N123" s="70"/>
-      <c r="O123" s="70"/>
-      <c r="P123" s="70"/>
-      <c r="Q123" s="70"/>
-      <c r="R123" s="70"/>
-      <c r="S123" s="70"/>
-      <c r="T123" s="70"/>
-      <c r="U123" s="71"/>
+      <c r="E123" s="50"/>
+      <c r="F123" s="50"/>
+      <c r="G123" s="50"/>
+      <c r="H123" s="50"/>
+      <c r="I123" s="50"/>
+      <c r="J123" s="50"/>
+      <c r="K123" s="50"/>
+      <c r="L123" s="50"/>
+      <c r="M123" s="50"/>
+      <c r="N123" s="50"/>
+      <c r="O123" s="50"/>
+      <c r="P123" s="50"/>
+      <c r="Q123" s="50"/>
+      <c r="R123" s="50"/>
+      <c r="S123" s="50"/>
+      <c r="T123" s="50"/>
+      <c r="U123" s="51"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="61"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="31" t="s">
         <v>176</v>
       </c>
       <c r="C124" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="72"/>
-      <c r="E124" s="73"/>
-      <c r="F124" s="73"/>
-      <c r="G124" s="73"/>
-      <c r="H124" s="73"/>
-      <c r="I124" s="73"/>
-      <c r="J124" s="73"/>
-      <c r="K124" s="73"/>
-      <c r="L124" s="73"/>
-      <c r="M124" s="73"/>
-      <c r="N124" s="73"/>
-      <c r="O124" s="73"/>
-      <c r="P124" s="73"/>
-      <c r="Q124" s="73"/>
-      <c r="R124" s="73"/>
-      <c r="S124" s="73"/>
-      <c r="T124" s="73"/>
-      <c r="U124" s="74"/>
+      <c r="D124" s="52"/>
+      <c r="E124" s="53"/>
+      <c r="F124" s="53"/>
+      <c r="G124" s="53"/>
+      <c r="H124" s="53"/>
+      <c r="I124" s="53"/>
+      <c r="J124" s="53"/>
+      <c r="K124" s="53"/>
+      <c r="L124" s="53"/>
+      <c r="M124" s="53"/>
+      <c r="N124" s="53"/>
+      <c r="O124" s="53"/>
+      <c r="P124" s="53"/>
+      <c r="Q124" s="53"/>
+      <c r="R124" s="53"/>
+      <c r="S124" s="53"/>
+      <c r="T124" s="53"/>
+      <c r="U124" s="54"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="61"/>
+      <c r="A125" s="62"/>
       <c r="B125" s="31" t="s">
         <v>177</v>
       </c>
       <c r="C125" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="D125" s="72"/>
-      <c r="E125" s="73"/>
-      <c r="F125" s="73"/>
-      <c r="G125" s="73"/>
-      <c r="H125" s="73"/>
-      <c r="I125" s="73"/>
-      <c r="J125" s="73"/>
-      <c r="K125" s="73"/>
-      <c r="L125" s="73"/>
-      <c r="M125" s="73"/>
-      <c r="N125" s="73"/>
-      <c r="O125" s="73"/>
-      <c r="P125" s="73"/>
-      <c r="Q125" s="73"/>
-      <c r="R125" s="73"/>
-      <c r="S125" s="73"/>
-      <c r="T125" s="73"/>
-      <c r="U125" s="74"/>
+      <c r="D125" s="52"/>
+      <c r="E125" s="53"/>
+      <c r="F125" s="53"/>
+      <c r="G125" s="53"/>
+      <c r="H125" s="53"/>
+      <c r="I125" s="53"/>
+      <c r="J125" s="53"/>
+      <c r="K125" s="53"/>
+      <c r="L125" s="53"/>
+      <c r="M125" s="53"/>
+      <c r="N125" s="53"/>
+      <c r="O125" s="53"/>
+      <c r="P125" s="53"/>
+      <c r="Q125" s="53"/>
+      <c r="R125" s="53"/>
+      <c r="S125" s="53"/>
+      <c r="T125" s="53"/>
+      <c r="U125" s="54"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="61"/>
+      <c r="A126" s="62"/>
       <c r="B126" s="31" t="s">
         <v>178</v>
       </c>
       <c r="C126" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="72"/>
-      <c r="E126" s="73"/>
-      <c r="F126" s="73"/>
-      <c r="G126" s="73"/>
-      <c r="H126" s="73"/>
-      <c r="I126" s="73"/>
-      <c r="J126" s="73"/>
-      <c r="K126" s="73"/>
-      <c r="L126" s="73"/>
-      <c r="M126" s="73"/>
-      <c r="N126" s="73"/>
-      <c r="O126" s="73"/>
-      <c r="P126" s="73"/>
-      <c r="Q126" s="73"/>
-      <c r="R126" s="73"/>
-      <c r="S126" s="73"/>
-      <c r="T126" s="73"/>
-      <c r="U126" s="74"/>
+      <c r="D126" s="52"/>
+      <c r="E126" s="53"/>
+      <c r="F126" s="53"/>
+      <c r="G126" s="53"/>
+      <c r="H126" s="53"/>
+      <c r="I126" s="53"/>
+      <c r="J126" s="53"/>
+      <c r="K126" s="53"/>
+      <c r="L126" s="53"/>
+      <c r="M126" s="53"/>
+      <c r="N126" s="53"/>
+      <c r="O126" s="53"/>
+      <c r="P126" s="53"/>
+      <c r="Q126" s="53"/>
+      <c r="R126" s="53"/>
+      <c r="S126" s="53"/>
+      <c r="T126" s="53"/>
+      <c r="U126" s="54"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="61"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="30" t="s">
         <v>179</v>
       </c>
       <c r="C127" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="D127" s="72"/>
-      <c r="E127" s="73"/>
-      <c r="F127" s="73"/>
-      <c r="G127" s="73"/>
-      <c r="H127" s="73"/>
-      <c r="I127" s="73"/>
-      <c r="J127" s="73"/>
-      <c r="K127" s="73"/>
-      <c r="L127" s="73"/>
-      <c r="M127" s="73"/>
-      <c r="N127" s="73"/>
-      <c r="O127" s="73"/>
-      <c r="P127" s="73"/>
-      <c r="Q127" s="73"/>
-      <c r="R127" s="73"/>
-      <c r="S127" s="73"/>
-      <c r="T127" s="73"/>
-      <c r="U127" s="74"/>
+      <c r="D127" s="52"/>
+      <c r="E127" s="53"/>
+      <c r="F127" s="53"/>
+      <c r="G127" s="53"/>
+      <c r="H127" s="53"/>
+      <c r="I127" s="53"/>
+      <c r="J127" s="53"/>
+      <c r="K127" s="53"/>
+      <c r="L127" s="53"/>
+      <c r="M127" s="53"/>
+      <c r="N127" s="53"/>
+      <c r="O127" s="53"/>
+      <c r="P127" s="53"/>
+      <c r="Q127" s="53"/>
+      <c r="R127" s="53"/>
+      <c r="S127" s="53"/>
+      <c r="T127" s="53"/>
+      <c r="U127" s="54"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="61"/>
+      <c r="A128" s="62"/>
       <c r="B128" s="31" t="s">
         <v>180</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D128" s="72"/>
-      <c r="E128" s="73"/>
-      <c r="F128" s="73"/>
-      <c r="G128" s="73"/>
-      <c r="H128" s="73"/>
-      <c r="I128" s="73"/>
-      <c r="J128" s="73"/>
-      <c r="K128" s="73"/>
-      <c r="L128" s="73"/>
-      <c r="M128" s="73"/>
-      <c r="N128" s="73"/>
-      <c r="O128" s="73"/>
-      <c r="P128" s="73"/>
-      <c r="Q128" s="73"/>
-      <c r="R128" s="73"/>
-      <c r="S128" s="73"/>
-      <c r="T128" s="73"/>
-      <c r="U128" s="74"/>
+        <v>39</v>
+      </c>
+      <c r="D128" s="52"/>
+      <c r="E128" s="53"/>
+      <c r="F128" s="53"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="53"/>
+      <c r="L128" s="53"/>
+      <c r="M128" s="53"/>
+      <c r="N128" s="53"/>
+      <c r="O128" s="53"/>
+      <c r="P128" s="53"/>
+      <c r="Q128" s="53"/>
+      <c r="R128" s="53"/>
+      <c r="S128" s="53"/>
+      <c r="T128" s="53"/>
+      <c r="U128" s="54"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="62"/>
+      <c r="A129" s="63"/>
       <c r="B129" s="31" t="s">
         <v>181</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D129" s="72"/>
-      <c r="E129" s="73"/>
-      <c r="F129" s="73"/>
-      <c r="G129" s="73"/>
-      <c r="H129" s="73"/>
-      <c r="I129" s="73"/>
-      <c r="J129" s="73"/>
-      <c r="K129" s="73"/>
-      <c r="L129" s="73"/>
-      <c r="M129" s="73"/>
-      <c r="N129" s="73"/>
-      <c r="O129" s="73"/>
-      <c r="P129" s="73"/>
-      <c r="Q129" s="73"/>
-      <c r="R129" s="73"/>
-      <c r="S129" s="73"/>
-      <c r="T129" s="73"/>
-      <c r="U129" s="74"/>
+        <v>43</v>
+      </c>
+      <c r="D129" s="52"/>
+      <c r="E129" s="53"/>
+      <c r="F129" s="53"/>
+      <c r="G129" s="53"/>
+      <c r="H129" s="53"/>
+      <c r="I129" s="53"/>
+      <c r="J129" s="53"/>
+      <c r="K129" s="53"/>
+      <c r="L129" s="53"/>
+      <c r="M129" s="53"/>
+      <c r="N129" s="53"/>
+      <c r="O129" s="53"/>
+      <c r="P129" s="53"/>
+      <c r="Q129" s="53"/>
+      <c r="R129" s="53"/>
+      <c r="S129" s="53"/>
+      <c r="T129" s="53"/>
+      <c r="U129" s="54"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="57">
+      <c r="A130" s="58">
         <v>19</v>
       </c>
       <c r="B130" s="33" t="s">
@@ -6557,186 +6575,186 @@
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="72"/>
-      <c r="E130" s="73"/>
-      <c r="F130" s="73"/>
-      <c r="G130" s="73"/>
-      <c r="H130" s="73"/>
-      <c r="I130" s="73"/>
-      <c r="J130" s="73"/>
-      <c r="K130" s="73"/>
-      <c r="L130" s="73"/>
-      <c r="M130" s="73"/>
-      <c r="N130" s="73"/>
-      <c r="O130" s="73"/>
-      <c r="P130" s="73"/>
-      <c r="Q130" s="73"/>
-      <c r="R130" s="73"/>
-      <c r="S130" s="73"/>
-      <c r="T130" s="73"/>
-      <c r="U130" s="74"/>
+      <c r="D130" s="52"/>
+      <c r="E130" s="53"/>
+      <c r="F130" s="53"/>
+      <c r="G130" s="53"/>
+      <c r="H130" s="53"/>
+      <c r="I130" s="53"/>
+      <c r="J130" s="53"/>
+      <c r="K130" s="53"/>
+      <c r="L130" s="53"/>
+      <c r="M130" s="53"/>
+      <c r="N130" s="53"/>
+      <c r="O130" s="53"/>
+      <c r="P130" s="53"/>
+      <c r="Q130" s="53"/>
+      <c r="R130" s="53"/>
+      <c r="S130" s="53"/>
+      <c r="T130" s="53"/>
+      <c r="U130" s="54"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="58"/>
+      <c r="A131" s="59"/>
       <c r="B131" s="33" t="s">
         <v>183</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="72"/>
-      <c r="E131" s="73"/>
-      <c r="F131" s="73"/>
-      <c r="G131" s="73"/>
-      <c r="H131" s="73"/>
-      <c r="I131" s="73"/>
-      <c r="J131" s="73"/>
-      <c r="K131" s="73"/>
-      <c r="L131" s="73"/>
-      <c r="M131" s="73"/>
-      <c r="N131" s="73"/>
-      <c r="O131" s="73"/>
-      <c r="P131" s="73"/>
-      <c r="Q131" s="73"/>
-      <c r="R131" s="73"/>
-      <c r="S131" s="73"/>
-      <c r="T131" s="73"/>
-      <c r="U131" s="74"/>
+      <c r="D131" s="52"/>
+      <c r="E131" s="53"/>
+      <c r="F131" s="53"/>
+      <c r="G131" s="53"/>
+      <c r="H131" s="53"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="53"/>
+      <c r="K131" s="53"/>
+      <c r="L131" s="53"/>
+      <c r="M131" s="53"/>
+      <c r="N131" s="53"/>
+      <c r="O131" s="53"/>
+      <c r="P131" s="53"/>
+      <c r="Q131" s="53"/>
+      <c r="R131" s="53"/>
+      <c r="S131" s="53"/>
+      <c r="T131" s="53"/>
+      <c r="U131" s="54"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="58"/>
+      <c r="A132" s="59"/>
       <c r="B132" s="33" t="s">
         <v>184</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D132" s="72"/>
-      <c r="E132" s="73"/>
-      <c r="F132" s="73"/>
-      <c r="G132" s="73"/>
-      <c r="H132" s="73"/>
-      <c r="I132" s="73"/>
-      <c r="J132" s="73"/>
-      <c r="K132" s="73"/>
-      <c r="L132" s="73"/>
-      <c r="M132" s="73"/>
-      <c r="N132" s="73"/>
-      <c r="O132" s="73"/>
-      <c r="P132" s="73"/>
-      <c r="Q132" s="73"/>
-      <c r="R132" s="73"/>
-      <c r="S132" s="73"/>
-      <c r="T132" s="73"/>
-      <c r="U132" s="74"/>
+      <c r="D132" s="52"/>
+      <c r="E132" s="53"/>
+      <c r="F132" s="53"/>
+      <c r="G132" s="53"/>
+      <c r="H132" s="53"/>
+      <c r="I132" s="53"/>
+      <c r="J132" s="53"/>
+      <c r="K132" s="53"/>
+      <c r="L132" s="53"/>
+      <c r="M132" s="53"/>
+      <c r="N132" s="53"/>
+      <c r="O132" s="53"/>
+      <c r="P132" s="53"/>
+      <c r="Q132" s="53"/>
+      <c r="R132" s="53"/>
+      <c r="S132" s="53"/>
+      <c r="T132" s="53"/>
+      <c r="U132" s="54"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="58"/>
+      <c r="A133" s="59"/>
       <c r="B133" s="33" t="s">
         <v>185</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="72"/>
-      <c r="E133" s="73"/>
-      <c r="F133" s="73"/>
-      <c r="G133" s="73"/>
-      <c r="H133" s="73"/>
-      <c r="I133" s="73"/>
-      <c r="J133" s="73"/>
-      <c r="K133" s="73"/>
-      <c r="L133" s="73"/>
-      <c r="M133" s="73"/>
-      <c r="N133" s="73"/>
-      <c r="O133" s="73"/>
-      <c r="P133" s="73"/>
-      <c r="Q133" s="73"/>
-      <c r="R133" s="73"/>
-      <c r="S133" s="73"/>
-      <c r="T133" s="73"/>
-      <c r="U133" s="74"/>
+      <c r="D133" s="52"/>
+      <c r="E133" s="53"/>
+      <c r="F133" s="53"/>
+      <c r="G133" s="53"/>
+      <c r="H133" s="53"/>
+      <c r="I133" s="53"/>
+      <c r="J133" s="53"/>
+      <c r="K133" s="53"/>
+      <c r="L133" s="53"/>
+      <c r="M133" s="53"/>
+      <c r="N133" s="53"/>
+      <c r="O133" s="53"/>
+      <c r="P133" s="53"/>
+      <c r="Q133" s="53"/>
+      <c r="R133" s="53"/>
+      <c r="S133" s="53"/>
+      <c r="T133" s="53"/>
+      <c r="U133" s="54"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="58"/>
+      <c r="A134" s="59"/>
       <c r="B134" s="33" t="s">
         <v>186</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D134" s="72"/>
-      <c r="E134" s="73"/>
-      <c r="F134" s="73"/>
-      <c r="G134" s="73"/>
-      <c r="H134" s="73"/>
-      <c r="I134" s="73"/>
-      <c r="J134" s="73"/>
-      <c r="K134" s="73"/>
-      <c r="L134" s="73"/>
-      <c r="M134" s="73"/>
-      <c r="N134" s="73"/>
-      <c r="O134" s="73"/>
-      <c r="P134" s="73"/>
-      <c r="Q134" s="73"/>
-      <c r="R134" s="73"/>
-      <c r="S134" s="73"/>
-      <c r="T134" s="73"/>
-      <c r="U134" s="74"/>
+      <c r="D134" s="52"/>
+      <c r="E134" s="53"/>
+      <c r="F134" s="53"/>
+      <c r="G134" s="53"/>
+      <c r="H134" s="53"/>
+      <c r="I134" s="53"/>
+      <c r="J134" s="53"/>
+      <c r="K134" s="53"/>
+      <c r="L134" s="53"/>
+      <c r="M134" s="53"/>
+      <c r="N134" s="53"/>
+      <c r="O134" s="53"/>
+      <c r="P134" s="53"/>
+      <c r="Q134" s="53"/>
+      <c r="R134" s="53"/>
+      <c r="S134" s="53"/>
+      <c r="T134" s="53"/>
+      <c r="U134" s="54"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="58"/>
+      <c r="A135" s="59"/>
       <c r="B135" s="33" t="s">
         <v>187</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D135" s="72"/>
-      <c r="E135" s="73"/>
-      <c r="F135" s="73"/>
-      <c r="G135" s="73"/>
-      <c r="H135" s="73"/>
-      <c r="I135" s="73"/>
-      <c r="J135" s="73"/>
-      <c r="K135" s="73"/>
-      <c r="L135" s="73"/>
-      <c r="M135" s="73"/>
-      <c r="N135" s="73"/>
-      <c r="O135" s="73"/>
-      <c r="P135" s="73"/>
-      <c r="Q135" s="73"/>
-      <c r="R135" s="73"/>
-      <c r="S135" s="73"/>
-      <c r="T135" s="73"/>
-      <c r="U135" s="74"/>
+        <v>39</v>
+      </c>
+      <c r="D135" s="52"/>
+      <c r="E135" s="53"/>
+      <c r="F135" s="53"/>
+      <c r="G135" s="53"/>
+      <c r="H135" s="53"/>
+      <c r="I135" s="53"/>
+      <c r="J135" s="53"/>
+      <c r="K135" s="53"/>
+      <c r="L135" s="53"/>
+      <c r="M135" s="53"/>
+      <c r="N135" s="53"/>
+      <c r="O135" s="53"/>
+      <c r="P135" s="53"/>
+      <c r="Q135" s="53"/>
+      <c r="R135" s="53"/>
+      <c r="S135" s="53"/>
+      <c r="T135" s="53"/>
+      <c r="U135" s="54"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="59"/>
+      <c r="A136" s="60"/>
       <c r="B136" s="33" t="s">
         <v>188</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D136" s="75"/>
-      <c r="E136" s="76"/>
-      <c r="F136" s="76"/>
-      <c r="G136" s="76"/>
-      <c r="H136" s="76"/>
-      <c r="I136" s="76"/>
-      <c r="J136" s="76"/>
-      <c r="K136" s="76"/>
-      <c r="L136" s="76"/>
-      <c r="M136" s="76"/>
-      <c r="N136" s="76"/>
-      <c r="O136" s="76"/>
-      <c r="P136" s="76"/>
-      <c r="Q136" s="76"/>
-      <c r="R136" s="76"/>
-      <c r="S136" s="76"/>
-      <c r="T136" s="76"/>
-      <c r="U136" s="77"/>
+        <v>43</v>
+      </c>
+      <c r="D136" s="55"/>
+      <c r="E136" s="56"/>
+      <c r="F136" s="56"/>
+      <c r="G136" s="56"/>
+      <c r="H136" s="56"/>
+      <c r="I136" s="56"/>
+      <c r="J136" s="56"/>
+      <c r="K136" s="56"/>
+      <c r="L136" s="56"/>
+      <c r="M136" s="56"/>
+      <c r="N136" s="56"/>
+      <c r="O136" s="56"/>
+      <c r="P136" s="56"/>
+      <c r="Q136" s="56"/>
+      <c r="R136" s="56"/>
+      <c r="S136" s="56"/>
+      <c r="T136" s="56"/>
+      <c r="U136" s="57"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6754,26 +6772,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6790,6 +6788,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
